--- a/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,25 +368,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_cost</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1_cost</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median_cost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3_cost</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -400,18 +410,24 @@
         <v>118.63</v>
       </c>
       <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>1712.67</v>
+      </c>
+      <c r="E2">
         <v>95.98999999999999</v>
       </c>
-      <c r="D2">
-        <v>42</v>
-      </c>
-      <c r="E2">
-        <v>84</v>
-      </c>
       <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>84</v>
+      </c>
+      <c r="H2">
         <v>168</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>18324</v>
       </c>
     </row>
@@ -423,18 +439,24 @@
         <v>103.19</v>
       </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>1164.77</v>
+      </c>
+      <c r="E3">
         <v>88.34999999999999</v>
       </c>
-      <c r="D3">
-        <v>42</v>
-      </c>
-      <c r="E3">
-        <v>84</v>
-      </c>
       <c r="F3">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G3">
+        <v>84</v>
+      </c>
+      <c r="H3">
+        <v>126</v>
+      </c>
+      <c r="I3">
         <v>15007</v>
       </c>
     </row>
@@ -446,18 +468,24 @@
         <v>102.71</v>
       </c>
       <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1078.73</v>
+      </c>
+      <c r="E4">
         <v>86.87</v>
       </c>
-      <c r="D4">
-        <v>42</v>
-      </c>
-      <c r="E4">
-        <v>84</v>
-      </c>
       <c r="F4">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>126</v>
+      </c>
+      <c r="I4">
         <v>13521</v>
       </c>
     </row>
@@ -469,18 +497,24 @@
         <v>97.73999999999999</v>
       </c>
       <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>1302</v>
+      </c>
+      <c r="E5">
         <v>81.73999999999999</v>
       </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <v>84</v>
-      </c>
       <c r="F5">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>126</v>
+      </c>
+      <c r="I5">
         <v>12297</v>
       </c>
     </row>
@@ -492,18 +526,24 @@
         <v>97.39</v>
       </c>
       <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>920.75</v>
+      </c>
+      <c r="E6">
         <v>81.48</v>
       </c>
-      <c r="D6">
-        <v>42</v>
-      </c>
-      <c r="E6">
-        <v>84</v>
-      </c>
       <c r="F6">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>126</v>
+      </c>
+      <c r="I6">
         <v>10837</v>
       </c>
     </row>
@@ -515,18 +555,24 @@
         <v>97.34999999999999</v>
       </c>
       <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1689.75</v>
+      </c>
+      <c r="E7">
         <v>83.2</v>
       </c>
-      <c r="D7">
-        <v>42</v>
-      </c>
-      <c r="E7">
-        <v>84</v>
-      </c>
       <c r="F7">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G7">
+        <v>84</v>
+      </c>
+      <c r="H7">
+        <v>126</v>
+      </c>
+      <c r="I7">
         <v>10023</v>
       </c>
     </row>
@@ -538,18 +584,24 @@
         <v>97.5</v>
       </c>
       <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>1034.75</v>
+      </c>
+      <c r="E8">
         <v>81.66</v>
       </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>84</v>
-      </c>
       <c r="F8">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G8">
+        <v>84</v>
+      </c>
+      <c r="H8">
+        <v>126</v>
+      </c>
+      <c r="I8">
         <v>9330</v>
       </c>
     </row>
@@ -561,18 +613,24 @@
         <v>94.67</v>
       </c>
       <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>1214.24</v>
+      </c>
+      <c r="E9">
         <v>78.23999999999999</v>
       </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>84</v>
-      </c>
       <c r="F9">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G9">
+        <v>84</v>
+      </c>
+      <c r="H9">
+        <v>126</v>
+      </c>
+      <c r="I9">
         <v>8918</v>
       </c>
     </row>
@@ -584,18 +642,24 @@
         <v>97.20999999999999</v>
       </c>
       <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>1344</v>
+      </c>
+      <c r="E10">
         <v>81</v>
       </c>
-      <c r="D10">
-        <v>42</v>
-      </c>
-      <c r="E10">
-        <v>84</v>
-      </c>
       <c r="F10">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
+        <v>126</v>
+      </c>
+      <c r="I10">
         <v>8562</v>
       </c>
     </row>
@@ -607,18 +671,24 @@
         <v>94.53</v>
       </c>
       <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>1382.24</v>
+      </c>
+      <c r="E11">
         <v>77.11</v>
       </c>
-      <c r="D11">
-        <v>42</v>
-      </c>
-      <c r="E11">
-        <v>84</v>
-      </c>
       <c r="F11">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G11">
+        <v>84</v>
+      </c>
+      <c r="H11">
+        <v>126</v>
+      </c>
+      <c r="I11">
         <v>8181</v>
       </c>
     </row>
@@ -630,18 +700,24 @@
         <v>95.02</v>
       </c>
       <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>1664.75</v>
+      </c>
+      <c r="E12">
         <v>78.20999999999999</v>
       </c>
-      <c r="D12">
-        <v>42</v>
-      </c>
-      <c r="E12">
-        <v>84</v>
-      </c>
       <c r="F12">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G12">
+        <v>84</v>
+      </c>
+      <c r="H12">
+        <v>126</v>
+      </c>
+      <c r="I12">
         <v>7905</v>
       </c>
     </row>
@@ -653,18 +729,24 @@
         <v>96.41</v>
       </c>
       <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>1282.98</v>
+      </c>
+      <c r="E13">
         <v>79.56999999999999</v>
       </c>
-      <c r="D13">
-        <v>42</v>
-      </c>
-      <c r="E13">
-        <v>84</v>
-      </c>
       <c r="F13">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G13">
+        <v>84</v>
+      </c>
+      <c r="H13">
+        <v>126</v>
+      </c>
+      <c r="I13">
         <v>7693</v>
       </c>
     </row>
@@ -676,18 +758,24 @@
         <v>95.23999999999999</v>
       </c>
       <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>882</v>
+      </c>
+      <c r="E14">
         <v>77.33</v>
       </c>
-      <c r="D14">
-        <v>42</v>
-      </c>
-      <c r="E14">
-        <v>84</v>
-      </c>
       <c r="F14">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G14">
+        <v>84</v>
+      </c>
+      <c r="H14">
+        <v>126</v>
+      </c>
+      <c r="I14">
         <v>7405</v>
       </c>
     </row>
@@ -699,18 +787,24 @@
         <v>95.87</v>
       </c>
       <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>1349.3</v>
+      </c>
+      <c r="E15">
         <v>79.65000000000001</v>
       </c>
-      <c r="D15">
-        <v>42</v>
-      </c>
-      <c r="E15">
-        <v>84</v>
-      </c>
       <c r="F15">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G15">
+        <v>84</v>
+      </c>
+      <c r="H15">
+        <v>126</v>
+      </c>
+      <c r="I15">
         <v>7053</v>
       </c>
     </row>
@@ -722,18 +816,24 @@
         <v>96.66</v>
       </c>
       <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>758</v>
+      </c>
+      <c r="E16">
         <v>79.03</v>
       </c>
-      <c r="D16">
-        <v>42</v>
-      </c>
-      <c r="E16">
-        <v>84</v>
-      </c>
       <c r="F16">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G16">
+        <v>84</v>
+      </c>
+      <c r="H16">
+        <v>126</v>
+      </c>
+      <c r="I16">
         <v>6818</v>
       </c>
     </row>
@@ -745,18 +845,24 @@
         <v>95.27</v>
       </c>
       <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>954.71</v>
+      </c>
+      <c r="E17">
         <v>78.77</v>
       </c>
-      <c r="D17">
-        <v>42</v>
-      </c>
-      <c r="E17">
-        <v>84</v>
-      </c>
       <c r="F17">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G17">
+        <v>84</v>
+      </c>
+      <c r="H17">
+        <v>126</v>
+      </c>
+      <c r="I17">
         <v>6550</v>
       </c>
     </row>
@@ -768,18 +874,24 @@
         <v>94.63</v>
       </c>
       <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>652.98</v>
+      </c>
+      <c r="E18">
         <v>74.64</v>
       </c>
-      <c r="D18">
-        <v>42</v>
-      </c>
-      <c r="E18">
-        <v>84</v>
-      </c>
       <c r="F18">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G18">
+        <v>84</v>
+      </c>
+      <c r="H18">
+        <v>126</v>
+      </c>
+      <c r="I18">
         <v>6392</v>
       </c>
     </row>
@@ -791,18 +903,24 @@
         <v>95.73999999999999</v>
       </c>
       <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>887.4</v>
+      </c>
+      <c r="E19">
         <v>80.52</v>
       </c>
-      <c r="D19">
-        <v>42</v>
-      </c>
-      <c r="E19">
-        <v>84</v>
-      </c>
       <c r="F19">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G19">
+        <v>84</v>
+      </c>
+      <c r="H19">
+        <v>126</v>
+      </c>
+      <c r="I19">
         <v>6156</v>
       </c>
     </row>
@@ -814,18 +932,24 @@
         <v>94.47</v>
       </c>
       <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>730.75</v>
+      </c>
+      <c r="E20">
         <v>77.69</v>
       </c>
-      <c r="D20">
-        <v>42</v>
-      </c>
-      <c r="E20">
-        <v>84</v>
-      </c>
       <c r="F20">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G20">
+        <v>84</v>
+      </c>
+      <c r="H20">
+        <v>126</v>
+      </c>
+      <c r="I20">
         <v>6001</v>
       </c>
     </row>
@@ -837,18 +961,24 @@
         <v>94.87</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>798</v>
+      </c>
+      <c r="E21">
         <v>78.53</v>
       </c>
-      <c r="D21">
-        <v>42</v>
-      </c>
-      <c r="E21">
+      <c r="F21">
+        <v>42</v>
+      </c>
+      <c r="G21">
         <v>80.39230000000001</v>
       </c>
-      <c r="F21">
-        <v>126</v>
-      </c>
-      <c r="G21">
+      <c r="H21">
+        <v>126</v>
+      </c>
+      <c r="I21">
         <v>5751</v>
       </c>
     </row>
@@ -860,18 +990,24 @@
         <v>95.83</v>
       </c>
       <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>908</v>
+      </c>
+      <c r="E22">
         <v>79.78</v>
       </c>
-      <c r="D22">
-        <v>42</v>
-      </c>
-      <c r="E22">
-        <v>84</v>
-      </c>
       <c r="F22">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G22">
+        <v>84</v>
+      </c>
+      <c r="H22">
+        <v>126</v>
+      </c>
+      <c r="I22">
         <v>5651</v>
       </c>
     </row>
@@ -883,18 +1019,24 @@
         <v>93.59999999999999</v>
       </c>
       <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>1028.35</v>
+      </c>
+      <c r="E23">
         <v>76.09999999999999</v>
       </c>
-      <c r="D23">
-        <v>42</v>
-      </c>
-      <c r="E23">
-        <v>84</v>
-      </c>
       <c r="F23">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G23">
+        <v>84</v>
+      </c>
+      <c r="H23">
+        <v>126</v>
+      </c>
+      <c r="I23">
         <v>5388</v>
       </c>
     </row>
@@ -906,18 +1048,24 @@
         <v>94.75</v>
       </c>
       <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>875.47</v>
+      </c>
+      <c r="E24">
         <v>77.56999999999999</v>
       </c>
-      <c r="D24">
-        <v>42</v>
-      </c>
-      <c r="E24">
-        <v>84</v>
-      </c>
       <c r="F24">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G24">
+        <v>84</v>
+      </c>
+      <c r="H24">
+        <v>126</v>
+      </c>
+      <c r="I24">
         <v>5228</v>
       </c>
     </row>
@@ -929,18 +1077,24 @@
         <v>95.20999999999999</v>
       </c>
       <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>756</v>
+      </c>
+      <c r="E25">
         <v>77.16</v>
       </c>
-      <c r="D25">
-        <v>42</v>
-      </c>
-      <c r="E25">
-        <v>84</v>
-      </c>
       <c r="F25">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G25">
+        <v>84</v>
+      </c>
+      <c r="H25">
+        <v>126</v>
+      </c>
+      <c r="I25">
         <v>4949</v>
       </c>
     </row>
@@ -952,18 +1106,24 @@
         <v>42.15</v>
       </c>
       <c r="C26">
+        <v>19.2</v>
+      </c>
+      <c r="D26">
+        <v>113.5</v>
+      </c>
+      <c r="E26">
         <v>11.87</v>
       </c>
-      <c r="D26">
-        <v>42</v>
-      </c>
-      <c r="E26">
-        <v>42</v>
-      </c>
       <c r="F26">
         <v>42</v>
       </c>
       <c r="G26">
+        <v>42</v>
+      </c>
+      <c r="H26">
+        <v>42</v>
+      </c>
+      <c r="I26">
         <v>157</v>
       </c>
     </row>
@@ -974,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -990,25 +1150,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_cost</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1_cost</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median_cost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3_cost</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -1022,18 +1192,24 @@
         <v>118.63</v>
       </c>
       <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>1712.67</v>
+      </c>
+      <c r="E2">
         <v>95.98999999999999</v>
       </c>
-      <c r="D2">
-        <v>42</v>
-      </c>
-      <c r="E2">
-        <v>84</v>
-      </c>
       <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>84</v>
+      </c>
+      <c r="H2">
         <v>168</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>18324</v>
       </c>
     </row>
@@ -1045,18 +1221,24 @@
         <v>103.45</v>
       </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>1164.77</v>
+      </c>
+      <c r="E3">
         <v>88.53</v>
       </c>
-      <c r="D3">
-        <v>42</v>
-      </c>
-      <c r="E3">
-        <v>84</v>
-      </c>
       <c r="F3">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G3">
+        <v>84</v>
+      </c>
+      <c r="H3">
+        <v>126</v>
+      </c>
+      <c r="I3">
         <v>14871</v>
       </c>
     </row>
@@ -1068,18 +1250,24 @@
         <v>102.88</v>
       </c>
       <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1078.73</v>
+      </c>
+      <c r="E4">
         <v>87</v>
       </c>
-      <c r="D4">
-        <v>42</v>
-      </c>
-      <c r="E4">
-        <v>84</v>
-      </c>
       <c r="F4">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>126</v>
+      </c>
+      <c r="I4">
         <v>13417</v>
       </c>
     </row>
@@ -1091,18 +1279,24 @@
         <v>99.25</v>
       </c>
       <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>1302</v>
+      </c>
+      <c r="E5">
         <v>82.59999999999999</v>
       </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <v>84</v>
-      </c>
       <c r="F5">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>126</v>
+      </c>
+      <c r="I5">
         <v>11768</v>
       </c>
     </row>
@@ -1114,18 +1308,24 @@
         <v>98</v>
       </c>
       <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>920.75</v>
+      </c>
+      <c r="E6">
         <v>81.77</v>
       </c>
-      <c r="D6">
-        <v>42</v>
-      </c>
-      <c r="E6">
-        <v>84</v>
-      </c>
       <c r="F6">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>126</v>
+      </c>
+      <c r="I6">
         <v>10615</v>
       </c>
     </row>
@@ -1137,18 +1337,24 @@
         <v>97.90000000000001</v>
       </c>
       <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1689.75</v>
+      </c>
+      <c r="E7">
         <v>83.56999999999999</v>
       </c>
-      <c r="D7">
-        <v>42</v>
-      </c>
-      <c r="E7">
-        <v>84</v>
-      </c>
       <c r="F7">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G7">
+        <v>84</v>
+      </c>
+      <c r="H7">
+        <v>126</v>
+      </c>
+      <c r="I7">
         <v>9848</v>
       </c>
     </row>
@@ -1160,18 +1366,24 @@
         <v>97.72</v>
       </c>
       <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>1034.75</v>
+      </c>
+      <c r="E8">
         <v>81.81999999999999</v>
       </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>84</v>
-      </c>
       <c r="F8">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G8">
+        <v>84</v>
+      </c>
+      <c r="H8">
+        <v>126</v>
+      </c>
+      <c r="I8">
         <v>9231</v>
       </c>
     </row>
@@ -1183,18 +1395,24 @@
         <v>94.90000000000001</v>
       </c>
       <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>1214.24</v>
+      </c>
+      <c r="E9">
         <v>78.40000000000001</v>
       </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>84</v>
-      </c>
       <c r="F9">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G9">
+        <v>84</v>
+      </c>
+      <c r="H9">
+        <v>126</v>
+      </c>
+      <c r="I9">
         <v>8815</v>
       </c>
     </row>
@@ -1206,18 +1424,24 @@
         <v>97.39</v>
       </c>
       <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>1344</v>
+      </c>
+      <c r="E10">
         <v>81.13</v>
       </c>
-      <c r="D10">
-        <v>42</v>
-      </c>
-      <c r="E10">
-        <v>84</v>
-      </c>
       <c r="F10">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
+        <v>126</v>
+      </c>
+      <c r="I10">
         <v>8481</v>
       </c>
     </row>
@@ -1229,18 +1453,24 @@
         <v>94.78</v>
       </c>
       <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>1382.24</v>
+      </c>
+      <c r="E11">
         <v>77.2</v>
       </c>
-      <c r="D11">
-        <v>42</v>
-      </c>
-      <c r="E11">
-        <v>84</v>
-      </c>
       <c r="F11">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G11">
+        <v>84</v>
+      </c>
+      <c r="H11">
+        <v>126</v>
+      </c>
+      <c r="I11">
         <v>8113</v>
       </c>
     </row>
@@ -1252,18 +1482,24 @@
         <v>95.20999999999999</v>
       </c>
       <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>1664.75</v>
+      </c>
+      <c r="E12">
         <v>78.34999999999999</v>
       </c>
-      <c r="D12">
-        <v>42</v>
-      </c>
-      <c r="E12">
-        <v>84</v>
-      </c>
       <c r="F12">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G12">
+        <v>84</v>
+      </c>
+      <c r="H12">
+        <v>126</v>
+      </c>
+      <c r="I12">
         <v>7841</v>
       </c>
     </row>
@@ -1275,18 +1511,24 @@
         <v>96.55</v>
       </c>
       <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>1282.98</v>
+      </c>
+      <c r="E13">
         <v>79.58</v>
       </c>
-      <c r="D13">
-        <v>42</v>
-      </c>
-      <c r="E13">
-        <v>84</v>
-      </c>
       <c r="F13">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G13">
+        <v>84</v>
+      </c>
+      <c r="H13">
+        <v>126</v>
+      </c>
+      <c r="I13">
         <v>7624</v>
       </c>
     </row>
@@ -1298,18 +1540,24 @@
         <v>95.37</v>
       </c>
       <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>882</v>
+      </c>
+      <c r="E14">
         <v>77.45999999999999</v>
       </c>
-      <c r="D14">
-        <v>42</v>
-      </c>
-      <c r="E14">
-        <v>84</v>
-      </c>
       <c r="F14">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G14">
+        <v>84</v>
+      </c>
+      <c r="H14">
+        <v>126</v>
+      </c>
+      <c r="I14">
         <v>7351</v>
       </c>
     </row>
@@ -1321,18 +1569,24 @@
         <v>95.97</v>
       </c>
       <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>1349.3</v>
+      </c>
+      <c r="E15">
         <v>79.76000000000001</v>
       </c>
-      <c r="D15">
-        <v>42</v>
-      </c>
-      <c r="E15">
-        <v>84</v>
-      </c>
       <c r="F15">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G15">
+        <v>84</v>
+      </c>
+      <c r="H15">
+        <v>126</v>
+      </c>
+      <c r="I15">
         <v>7013</v>
       </c>
     </row>
@@ -1344,18 +1598,24 @@
         <v>96.78</v>
       </c>
       <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>758</v>
+      </c>
+      <c r="E16">
         <v>79.13</v>
       </c>
-      <c r="D16">
-        <v>42</v>
-      </c>
-      <c r="E16">
-        <v>84</v>
-      </c>
       <c r="F16">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G16">
+        <v>84</v>
+      </c>
+      <c r="H16">
+        <v>126</v>
+      </c>
+      <c r="I16">
         <v>6768</v>
       </c>
     </row>
@@ -1367,18 +1627,24 @@
         <v>95.38</v>
       </c>
       <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>954.71</v>
+      </c>
+      <c r="E17">
         <v>78.76000000000001</v>
       </c>
-      <c r="D17">
-        <v>42</v>
-      </c>
-      <c r="E17">
-        <v>84</v>
-      </c>
       <c r="F17">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G17">
+        <v>84</v>
+      </c>
+      <c r="H17">
+        <v>126</v>
+      </c>
+      <c r="I17">
         <v>6499</v>
       </c>
     </row>
@@ -1390,18 +1656,24 @@
         <v>94.77</v>
       </c>
       <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>652.98</v>
+      </c>
+      <c r="E18">
         <v>74.56999999999999</v>
       </c>
-      <c r="D18">
-        <v>42</v>
-      </c>
-      <c r="E18">
-        <v>84</v>
-      </c>
       <c r="F18">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G18">
+        <v>84</v>
+      </c>
+      <c r="H18">
+        <v>126</v>
+      </c>
+      <c r="I18">
         <v>6348</v>
       </c>
     </row>
@@ -1413,18 +1685,24 @@
         <v>95.84999999999999</v>
       </c>
       <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>887.4</v>
+      </c>
+      <c r="E19">
         <v>80.63</v>
       </c>
-      <c r="D19">
-        <v>42</v>
-      </c>
-      <c r="E19">
-        <v>84</v>
-      </c>
       <c r="F19">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G19">
+        <v>84</v>
+      </c>
+      <c r="H19">
+        <v>126</v>
+      </c>
+      <c r="I19">
         <v>6118</v>
       </c>
     </row>
@@ -1436,18 +1714,24 @@
         <v>94.56</v>
       </c>
       <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>730.75</v>
+      </c>
+      <c r="E20">
         <v>77.73999999999999</v>
       </c>
-      <c r="D20">
-        <v>42</v>
-      </c>
-      <c r="E20">
-        <v>84</v>
-      </c>
       <c r="F20">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G20">
+        <v>84</v>
+      </c>
+      <c r="H20">
+        <v>126</v>
+      </c>
+      <c r="I20">
         <v>5969</v>
       </c>
     </row>
@@ -1459,18 +1743,24 @@
         <v>94.84999999999999</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>798</v>
+      </c>
+      <c r="E21">
         <v>78.51000000000001</v>
       </c>
-      <c r="D21">
-        <v>42</v>
-      </c>
-      <c r="E21">
-        <v>80.39</v>
-      </c>
       <c r="F21">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G21">
+        <v>80.39230000000001</v>
+      </c>
+      <c r="H21">
+        <v>126</v>
+      </c>
+      <c r="I21">
         <v>5720</v>
       </c>
     </row>
@@ -1482,18 +1772,24 @@
         <v>95.88</v>
       </c>
       <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>882</v>
+      </c>
+      <c r="E22">
         <v>79.2</v>
       </c>
-      <c r="D22">
-        <v>42</v>
-      </c>
-      <c r="E22">
-        <v>84</v>
-      </c>
       <c r="F22">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G22">
+        <v>84</v>
+      </c>
+      <c r="H22">
+        <v>126</v>
+      </c>
+      <c r="I22">
         <v>5616</v>
       </c>
     </row>
@@ -1505,18 +1801,24 @@
         <v>93.69</v>
       </c>
       <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>1028.35</v>
+      </c>
+      <c r="E23">
         <v>76.23999999999999</v>
       </c>
-      <c r="D23">
-        <v>42</v>
-      </c>
-      <c r="E23">
-        <v>84</v>
-      </c>
       <c r="F23">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G23">
+        <v>84</v>
+      </c>
+      <c r="H23">
+        <v>126</v>
+      </c>
+      <c r="I23">
         <v>5352</v>
       </c>
     </row>
@@ -1528,18 +1830,24 @@
         <v>94.95</v>
       </c>
       <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>875.47</v>
+      </c>
+      <c r="E24">
         <v>77.67</v>
       </c>
-      <c r="D24">
-        <v>42</v>
-      </c>
-      <c r="E24">
-        <v>84</v>
-      </c>
       <c r="F24">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G24">
+        <v>84</v>
+      </c>
+      <c r="H24">
+        <v>126</v>
+      </c>
+      <c r="I24">
         <v>5205</v>
       </c>
     </row>
@@ -1551,18 +1859,24 @@
         <v>95.29000000000001</v>
       </c>
       <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>756</v>
+      </c>
+      <c r="E25">
         <v>77.25</v>
       </c>
-      <c r="D25">
-        <v>42</v>
-      </c>
-      <c r="E25">
-        <v>84</v>
-      </c>
       <c r="F25">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G25">
+        <v>84</v>
+      </c>
+      <c r="H25">
+        <v>126</v>
+      </c>
+      <c r="I25">
         <v>4920</v>
       </c>
     </row>
@@ -1574,18 +1888,24 @@
         <v>38.2</v>
       </c>
       <c r="C26">
+        <v>19.2</v>
+      </c>
+      <c r="D26">
+        <v>42</v>
+      </c>
+      <c r="E26">
         <v>9.31</v>
       </c>
-      <c r="D26">
-        <v>42</v>
-      </c>
-      <c r="E26">
-        <v>42</v>
-      </c>
       <c r="F26">
         <v>42</v>
       </c>
       <c r="G26">
+        <v>42</v>
+      </c>
+      <c r="H26">
+        <v>42</v>
+      </c>
+      <c r="I26">
         <v>6</v>
       </c>
     </row>

--- a/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,10 +404,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>118.63</v>
+        <v>119.85</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -416,7 +416,7 @@
         <v>1712.67</v>
       </c>
       <c r="E2">
-        <v>95.98999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -428,15 +428,15 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>18324</v>
+        <v>18397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>103.19</v>
+        <v>102.45</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -445,7 +445,7 @@
         <v>1164.77</v>
       </c>
       <c r="E3">
-        <v>88.34999999999999</v>
+        <v>87.62</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -457,15 +457,15 @@
         <v>126</v>
       </c>
       <c r="I3">
-        <v>15007</v>
+        <v>14899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>102.71</v>
+        <v>103.84</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -474,7 +474,7 @@
         <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>86.87</v>
+        <v>87.92</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -486,24 +486,24 @@
         <v>126</v>
       </c>
       <c r="I4">
-        <v>13521</v>
+        <v>13603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>97.73999999999999</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>1302</v>
+        <v>1260</v>
       </c>
       <c r="E5">
-        <v>81.73999999999999</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -515,15 +515,15 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>12297</v>
+        <v>12172</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>97.39</v>
+        <v>98.27</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -532,7 +532,7 @@
         <v>920.75</v>
       </c>
       <c r="E6">
-        <v>81.48</v>
+        <v>82.53</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -544,15 +544,15 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>10837</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>97.34999999999999</v>
+        <v>96.66</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -561,7 +561,7 @@
         <v>1689.75</v>
       </c>
       <c r="E7">
-        <v>83.2</v>
+        <v>82.33</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -573,24 +573,24 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>10023</v>
+        <v>9958</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>97.5</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1034.75</v>
+        <v>1076.75</v>
       </c>
       <c r="E8">
-        <v>81.66</v>
+        <v>83.02</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -602,15 +602,15 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>9330</v>
+        <v>9390</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>94.67</v>
+        <v>94.12</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -619,36 +619,36 @@
         <v>1214.24</v>
       </c>
       <c r="E9">
-        <v>78.23999999999999</v>
+        <v>77.47</v>
       </c>
       <c r="F9">
         <v>42</v>
       </c>
       <c r="G9">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H9">
         <v>126</v>
       </c>
       <c r="I9">
-        <v>8918</v>
+        <v>8834</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>97.20999999999999</v>
+        <v>96.37</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1344</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>81</v>
+        <v>80.42</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -660,24 +660,24 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>8562</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>94.53</v>
+        <v>95.5</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11">
-        <v>1382.24</v>
+        <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>77.11</v>
+        <v>77.84</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -689,24 +689,24 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>8181</v>
+        <v>8229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>95.02</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>1664.75</v>
+        <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>78.20999999999999</v>
+        <v>77.53</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -718,24 +718,24 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>7905</v>
+        <v>7828</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>96.41</v>
+        <v>97.5</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13">
-        <v>1282.98</v>
+        <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>79.56999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -747,15 +747,15 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>7693</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>95.23999999999999</v>
+        <v>94.61</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -764,7 +764,7 @@
         <v>882</v>
       </c>
       <c r="E14">
-        <v>77.33</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -776,24 +776,24 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>7405</v>
+        <v>7336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>95.87</v>
+        <v>96.67</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>1349.3</v>
+        <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>79.65000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -805,15 +805,15 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>7053</v>
+        <v>7102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>96.66</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -822,7 +822,7 @@
         <v>758</v>
       </c>
       <c r="E16">
-        <v>79.03</v>
+        <v>78.66</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -834,24 +834,24 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>6818</v>
+        <v>6745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>95.27</v>
+        <v>95.59</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>954.71</v>
+        <v>912.71</v>
       </c>
       <c r="E17">
-        <v>78.77</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="F17">
         <v>42</v>
@@ -863,24 +863,24 @@
         <v>126</v>
       </c>
       <c r="I17">
-        <v>6550</v>
+        <v>6597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>94.63</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>652.98</v>
+        <v>710.39</v>
       </c>
       <c r="E18">
-        <v>74.64</v>
+        <v>74.42</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -892,24 +892,24 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>6392</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>95.73999999999999</v>
+        <v>95.11</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>887.4</v>
+        <v>929.4</v>
       </c>
       <c r="E19">
-        <v>80.52</v>
+        <v>80.02</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -921,24 +921,24 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>6156</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>94.47</v>
+        <v>95.37</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>730.75</v>
+        <v>736.98</v>
       </c>
       <c r="E20">
-        <v>77.69</v>
+        <v>78.92</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -950,15 +950,15 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>6001</v>
+        <v>6024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>94.87</v>
+        <v>93.75</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -967,7 +967,7 @@
         <v>798</v>
       </c>
       <c r="E21">
-        <v>78.53</v>
+        <v>77.09</v>
       </c>
       <c r="F21">
         <v>42</v>
@@ -979,15 +979,15 @@
         <v>126</v>
       </c>
       <c r="I21">
-        <v>5751</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>95.83</v>
+        <v>96.81</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -996,7 +996,7 @@
         <v>908</v>
       </c>
       <c r="E22">
-        <v>79.78</v>
+        <v>80.88</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1008,15 +1008,15 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>5651</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>93.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -1025,7 +1025,7 @@
         <v>1028.35</v>
       </c>
       <c r="E23">
-        <v>76.09999999999999</v>
+        <v>75.67</v>
       </c>
       <c r="F23">
         <v>42</v>
@@ -1037,15 +1037,15 @@
         <v>126</v>
       </c>
       <c r="I23">
-        <v>5388</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>94.75</v>
+        <v>95.91</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -1054,7 +1054,7 @@
         <v>875.47</v>
       </c>
       <c r="E24">
-        <v>77.56999999999999</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1066,15 +1066,15 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>5228</v>
+        <v>5305</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>95.20999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -1083,7 +1083,7 @@
         <v>756</v>
       </c>
       <c r="E25">
-        <v>77.16</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F25">
         <v>42</v>
@@ -1095,36 +1095,7 @@
         <v>126</v>
       </c>
       <c r="I25">
-        <v>4949</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>42.15</v>
-      </c>
-      <c r="C26">
-        <v>19.2</v>
-      </c>
-      <c r="D26">
-        <v>113.5</v>
-      </c>
-      <c r="E26">
-        <v>11.87</v>
-      </c>
-      <c r="F26">
-        <v>42</v>
-      </c>
-      <c r="G26">
-        <v>42</v>
-      </c>
-      <c r="H26">
-        <v>42</v>
-      </c>
-      <c r="I26">
-        <v>157</v>
+        <v>4859</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1186,10 +1157,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>118.63</v>
+        <v>119.85</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -1198,7 +1169,7 @@
         <v>1712.67</v>
       </c>
       <c r="E2">
-        <v>95.98999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -1210,15 +1181,15 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>18324</v>
+        <v>18397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>103.45</v>
+        <v>102.6</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -1227,7 +1198,7 @@
         <v>1164.77</v>
       </c>
       <c r="E3">
-        <v>88.53</v>
+        <v>87.64</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -1239,15 +1210,15 @@
         <v>126</v>
       </c>
       <c r="I3">
-        <v>14871</v>
+        <v>14586</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>102.88</v>
+        <v>103.85</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -1256,7 +1227,7 @@
         <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>87</v>
+        <v>87.84</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -1268,24 +1239,24 @@
         <v>126</v>
       </c>
       <c r="I4">
-        <v>13417</v>
+        <v>13322</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>99.25</v>
+        <v>98.97</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>1302</v>
+        <v>1260</v>
       </c>
       <c r="E5">
-        <v>82.59999999999999</v>
+        <v>81.62</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -1297,24 +1268,24 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>11768</v>
+        <v>11204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>98</v>
+        <v>99.17</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>920.75</v>
+        <v>895.49</v>
       </c>
       <c r="E6">
-        <v>81.77</v>
+        <v>82.58</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -1326,15 +1297,15 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>10615</v>
+        <v>10401</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>97.90000000000001</v>
+        <v>97.11</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1343,7 +1314,7 @@
         <v>1689.75</v>
       </c>
       <c r="E7">
-        <v>83.56999999999999</v>
+        <v>82.75</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -1355,24 +1326,24 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>9848</v>
+        <v>9636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>97.72</v>
+        <v>98.44</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1034.75</v>
+        <v>1076.75</v>
       </c>
       <c r="E8">
-        <v>81.81999999999999</v>
+        <v>83.17</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -1384,15 +1355,15 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>9231</v>
+        <v>9155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>94.90000000000001</v>
+        <v>94.19</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1401,7 +1372,7 @@
         <v>1214.24</v>
       </c>
       <c r="E9">
-        <v>78.40000000000001</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="F9">
         <v>42</v>
@@ -1413,24 +1384,24 @@
         <v>126</v>
       </c>
       <c r="I9">
-        <v>8815</v>
+        <v>8626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>97.39</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1344</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>81.13</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -1442,24 +1413,24 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>8481</v>
+        <v>8367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>94.78</v>
+        <v>95.84</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11">
-        <v>1382.24</v>
+        <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>77.2</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -1471,24 +1442,24 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>8113</v>
+        <v>8071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>95.20999999999999</v>
+        <v>94.75</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>1664.75</v>
+        <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>78.34999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -1500,24 +1471,24 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>7841</v>
+        <v>7710</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>96.55</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13">
-        <v>1282.98</v>
+        <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>79.58</v>
+        <v>80.83</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -1529,15 +1500,15 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>7624</v>
+        <v>7619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>95.37</v>
+        <v>94.42</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1546,7 +1517,7 @@
         <v>882</v>
       </c>
       <c r="E14">
-        <v>77.45999999999999</v>
+        <v>76</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -1558,24 +1529,24 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>7351</v>
+        <v>7222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>95.97</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>1349.3</v>
+        <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>79.76000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -1587,15 +1558,15 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>7013</v>
+        <v>6998</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>96.78</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1604,7 +1575,7 @@
         <v>758</v>
       </c>
       <c r="E16">
-        <v>79.13</v>
+        <v>78.72</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -1616,24 +1587,24 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>6768</v>
+        <v>6637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>95.38</v>
+        <v>95.61</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>954.71</v>
+        <v>912.71</v>
       </c>
       <c r="E17">
-        <v>78.76000000000001</v>
+        <v>79.09</v>
       </c>
       <c r="F17">
         <v>42</v>
@@ -1645,24 +1616,24 @@
         <v>126</v>
       </c>
       <c r="I17">
-        <v>6499</v>
+        <v>6492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>94.77</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>652.98</v>
+        <v>710.39</v>
       </c>
       <c r="E18">
-        <v>74.56999999999999</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -1674,24 +1645,24 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>6348</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>95.84999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>887.4</v>
+        <v>929.4</v>
       </c>
       <c r="E19">
-        <v>80.63</v>
+        <v>80.27</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -1703,24 +1674,24 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>6118</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>94.56</v>
+        <v>95.47</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>730.75</v>
+        <v>736.98</v>
       </c>
       <c r="E20">
-        <v>77.73999999999999</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -1732,15 +1703,15 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>5969</v>
+        <v>5952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>94.84999999999999</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -1749,7 +1720,7 @@
         <v>798</v>
       </c>
       <c r="E21">
-        <v>78.51000000000001</v>
+        <v>76.88</v>
       </c>
       <c r="F21">
         <v>42</v>
@@ -1761,15 +1732,15 @@
         <v>126</v>
       </c>
       <c r="I21">
-        <v>5720</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>95.88</v>
+        <v>96.62</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -1778,7 +1749,7 @@
         <v>882</v>
       </c>
       <c r="E22">
-        <v>79.2</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1790,15 +1761,15 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>5616</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>93.69</v>
+        <v>93.25</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -1807,7 +1778,7 @@
         <v>1028.35</v>
       </c>
       <c r="E23">
-        <v>76.23999999999999</v>
+        <v>75.73</v>
       </c>
       <c r="F23">
         <v>42</v>
@@ -1819,15 +1790,15 @@
         <v>126</v>
       </c>
       <c r="I23">
-        <v>5352</v>
+        <v>5258</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>94.95</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -1836,7 +1807,7 @@
         <v>875.47</v>
       </c>
       <c r="E24">
-        <v>77.67</v>
+        <v>78.06</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1848,65 +1819,7 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>5205</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>95.29000000000001</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-      <c r="D25">
-        <v>756</v>
-      </c>
-      <c r="E25">
-        <v>77.25</v>
-      </c>
-      <c r="F25">
-        <v>42</v>
-      </c>
-      <c r="G25">
-        <v>84</v>
-      </c>
-      <c r="H25">
-        <v>126</v>
-      </c>
-      <c r="I25">
-        <v>4920</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>38.2</v>
-      </c>
-      <c r="C26">
-        <v>19.2</v>
-      </c>
-      <c r="D26">
-        <v>42</v>
-      </c>
-      <c r="E26">
-        <v>9.31</v>
-      </c>
-      <c r="F26">
-        <v>42</v>
-      </c>
-      <c r="G26">
-        <v>42</v>
-      </c>
-      <c r="H26">
-        <v>42</v>
-      </c>
-      <c r="I26">
-        <v>6</v>
+        <v>5249</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
@@ -407,16 +407,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>119.85</v>
+        <v>120.61</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>1712.67</v>
+        <v>1213.1</v>
       </c>
       <c r="E2">
-        <v>97.36</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -428,7 +428,7 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>18397</v>
+        <v>18396</v>
       </c>
     </row>
     <row r="3">
@@ -436,16 +436,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>102.45</v>
+        <v>103.62</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1164.77</v>
+        <v>871.26</v>
       </c>
       <c r="E3">
-        <v>87.62</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -457,7 +457,7 @@
         <v>126</v>
       </c>
       <c r="I3">
-        <v>14899</v>
+        <v>14967</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>103.84</v>
+        <v>105.66</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -474,7 +474,7 @@
         <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>87.92</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -486,7 +486,7 @@
         <v>126</v>
       </c>
       <c r="I4">
-        <v>13603</v>
+        <v>13635</v>
       </c>
     </row>
     <row r="5">
@@ -494,16 +494,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>96.81999999999999</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>1260</v>
+        <v>1735.8</v>
       </c>
       <c r="E5">
-        <v>80.54000000000001</v>
+        <v>83.97</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -515,7 +515,7 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>12172</v>
+        <v>12226</v>
       </c>
     </row>
     <row r="6">
@@ -523,16 +523,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>98.27</v>
+        <v>100.58</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>920.75</v>
+        <v>1242.08</v>
       </c>
       <c r="E6">
-        <v>82.53</v>
+        <v>86.67</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -544,7 +544,7 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>10899</v>
+        <v>10968</v>
       </c>
     </row>
     <row r="7">
@@ -552,16 +552,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>96.66</v>
+        <v>98.97</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>1689.75</v>
+        <v>1963.94</v>
       </c>
       <c r="E7">
-        <v>82.33</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -573,7 +573,7 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>9958</v>
+        <v>10006</v>
       </c>
     </row>
     <row r="8">
@@ -581,16 +581,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>98.31999999999999</v>
+        <v>100.11</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1076.75</v>
+        <v>1139.72</v>
       </c>
       <c r="E8">
-        <v>83.02</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -602,7 +602,7 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>9390</v>
+        <v>9483</v>
       </c>
     </row>
     <row r="9">
@@ -610,28 +610,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>94.12</v>
+        <v>96.2</v>
       </c>
       <c r="C9">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>1214.24</v>
+        <v>1276.66</v>
       </c>
       <c r="E9">
-        <v>77.47</v>
+        <v>81.69</v>
       </c>
       <c r="F9">
         <v>42</v>
       </c>
       <c r="G9">
-        <v>83</v>
+        <v>80.39230000000001</v>
       </c>
       <c r="H9">
         <v>126</v>
       </c>
       <c r="I9">
-        <v>8834</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="10">
@@ -639,16 +639,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>96.37</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>1909.94</v>
       </c>
       <c r="E10">
-        <v>80.42</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -660,7 +660,7 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>8539</v>
+        <v>8646</v>
       </c>
     </row>
     <row r="11">
@@ -668,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>95.5</v>
+        <v>97.53</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -677,7 +677,7 @@
         <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>77.84</v>
+        <v>81.09</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -689,7 +689,7 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>8229</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +697,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>94.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -706,7 +706,7 @@
         <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>77.53</v>
+        <v>81.25</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -718,7 +718,7 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>7828</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>97.5</v>
+        <v>99.52</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>80.91</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -747,7 +747,7 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>7774</v>
+        <v>7824</v>
       </c>
     </row>
     <row r="14">
@@ -755,16 +755,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>94.61</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>882</v>
+        <v>1470.92</v>
       </c>
       <c r="E14">
-        <v>76.45999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -776,7 +776,7 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>7336</v>
+        <v>7375</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +784,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>96.67</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -793,7 +793,7 @@
         <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>80.65000000000001</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -805,7 +805,7 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>7102</v>
+        <v>7187</v>
       </c>
     </row>
     <row r="16">
@@ -813,16 +813,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>96.43000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
       <c r="D16">
-        <v>758</v>
+        <v>823.72</v>
       </c>
       <c r="E16">
-        <v>78.66</v>
+        <v>82.87</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -834,7 +834,7 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>6745</v>
+        <v>6824</v>
       </c>
     </row>
     <row r="17">
@@ -842,28 +842,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>95.59</v>
+        <v>96.92</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>912.71</v>
+        <v>870.71</v>
       </c>
       <c r="E17">
-        <v>79.18000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="F17">
         <v>42</v>
       </c>
       <c r="G17">
-        <v>84</v>
+        <v>80.39230000000001</v>
       </c>
       <c r="H17">
         <v>126</v>
       </c>
       <c r="I17">
-        <v>6597</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="18">
@@ -871,16 +871,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>94.15000000000001</v>
+        <v>96.28</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>710.39</v>
+        <v>778.98</v>
       </c>
       <c r="E18">
-        <v>74.42</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -892,7 +892,7 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>6328</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="19">
@@ -900,16 +900,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>95.11</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>929.4</v>
+        <v>1284.08</v>
       </c>
       <c r="E19">
-        <v>80.02</v>
+        <v>85.19</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -921,7 +921,7 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>6141</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="20">
@@ -929,16 +929,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>95.37</v>
+        <v>97.7</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>736.98</v>
+        <v>1136.64</v>
       </c>
       <c r="E20">
-        <v>78.92</v>
+        <v>83.45</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -950,7 +950,7 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>6024</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="21">
@@ -958,28 +958,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>93.75</v>
+        <v>95.84</v>
       </c>
       <c r="C21">
         <v>6</v>
       </c>
       <c r="D21">
-        <v>798</v>
+        <v>768.04</v>
       </c>
       <c r="E21">
-        <v>77.09</v>
+        <v>80.2</v>
       </c>
       <c r="F21">
         <v>42</v>
       </c>
       <c r="G21">
-        <v>80.39230000000001</v>
+        <v>76.7846</v>
       </c>
       <c r="H21">
         <v>126</v>
       </c>
       <c r="I21">
-        <v>5719</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="22">
@@ -987,16 +987,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>96.81</v>
+        <v>98.87</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22">
-        <v>908</v>
+        <v>1004.65</v>
       </c>
       <c r="E22">
-        <v>80.88</v>
+        <v>85.77</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1008,7 +1008,7 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>5703</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="23">
@@ -1016,28 +1016,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>93.2</v>
+        <v>95.41</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>1028.35</v>
+        <v>840</v>
       </c>
       <c r="E23">
-        <v>75.67</v>
+        <v>79.95</v>
       </c>
       <c r="F23">
         <v>42</v>
       </c>
       <c r="G23">
-        <v>84</v>
+        <v>80.39230000000001</v>
       </c>
       <c r="H23">
         <v>126</v>
       </c>
       <c r="I23">
-        <v>5333</v>
+        <v>5406</v>
       </c>
     </row>
     <row r="24">
@@ -1045,16 +1045,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>95.91</v>
+        <v>97.69</v>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24">
-        <v>875.47</v>
+        <v>1045.53</v>
       </c>
       <c r="E24">
-        <v>78.15000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1066,7 +1066,7 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>5305</v>
+        <v>5358</v>
       </c>
     </row>
     <row r="25">
@@ -1074,16 +1074,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>94.33</v>
+        <v>95.09</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25">
-        <v>756</v>
+        <v>775.2</v>
       </c>
       <c r="E25">
-        <v>76.73999999999999</v>
+        <v>79.08</v>
       </c>
       <c r="F25">
         <v>42</v>
@@ -1095,7 +1095,7 @@
         <v>126</v>
       </c>
       <c r="I25">
-        <v>4859</v>
+        <v>4954</v>
       </c>
     </row>
   </sheetData>
@@ -1160,16 +1160,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>119.85</v>
+        <v>120.61</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>1712.67</v>
+        <v>1213.1</v>
       </c>
       <c r="E2">
-        <v>97.36</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -1181,7 +1181,7 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>18397</v>
+        <v>18396</v>
       </c>
     </row>
     <row r="3">
@@ -1189,16 +1189,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>102.6</v>
+        <v>103.8</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1164.77</v>
+        <v>871.26</v>
       </c>
       <c r="E3">
-        <v>87.64</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -1210,7 +1210,7 @@
         <v>126</v>
       </c>
       <c r="I3">
-        <v>14586</v>
+        <v>14651</v>
       </c>
     </row>
     <row r="4">
@@ -1218,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>103.85</v>
+        <v>105.64</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -1227,7 +1227,7 @@
         <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>87.84</v>
+        <v>90.47</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -1239,7 +1239,7 @@
         <v>126</v>
       </c>
       <c r="I4">
-        <v>13322</v>
+        <v>13352</v>
       </c>
     </row>
     <row r="5">
@@ -1247,16 +1247,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>98.97</v>
+        <v>100.57</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>1260</v>
+        <v>1735.8</v>
       </c>
       <c r="E5">
-        <v>81.62</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -1268,7 +1268,7 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>11204</v>
+        <v>11304</v>
       </c>
     </row>
     <row r="6">
@@ -1276,16 +1276,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>99.17</v>
+        <v>101.44</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>895.49</v>
+        <v>1242.08</v>
       </c>
       <c r="E6">
-        <v>82.58</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -1297,7 +1297,7 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>10401</v>
+        <v>10493</v>
       </c>
     </row>
     <row r="7">
@@ -1305,16 +1305,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>97.11</v>
+        <v>99.45</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>1689.75</v>
+        <v>1963.94</v>
       </c>
       <c r="E7">
-        <v>82.75</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -1326,7 +1326,7 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>9636</v>
+        <v>9694</v>
       </c>
     </row>
     <row r="8">
@@ -1334,16 +1334,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>98.44</v>
+        <v>100.3</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1076.75</v>
+        <v>1139.72</v>
       </c>
       <c r="E8">
-        <v>83.17</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -1355,7 +1355,7 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>9155</v>
+        <v>9248</v>
       </c>
     </row>
     <row r="9">
@@ -1363,28 +1363,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>94.19</v>
+        <v>96.25</v>
       </c>
       <c r="C9">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>1214.24</v>
+        <v>1276.66</v>
       </c>
       <c r="E9">
-        <v>77.48999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="F9">
         <v>42</v>
       </c>
       <c r="G9">
-        <v>84</v>
+        <v>80.39230000000001</v>
       </c>
       <c r="H9">
         <v>126</v>
       </c>
       <c r="I9">
-        <v>8626</v>
+        <v>8750</v>
       </c>
     </row>
     <row r="10">
@@ -1392,16 +1392,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>96.48999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>1909.94</v>
       </c>
       <c r="E10">
-        <v>80.59999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -1413,7 +1413,7 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>8367</v>
+        <v>8476</v>
       </c>
     </row>
     <row r="11">
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>95.84</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1430,7 +1430,7 @@
         <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>78.06999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -1442,7 +1442,7 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>8071</v>
+        <v>8152</v>
       </c>
     </row>
     <row r="12">
@@ -1450,7 +1450,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>94.75</v>
+        <v>96.88</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1459,7 +1459,7 @@
         <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>77.59999999999999</v>
+        <v>81.38</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -1471,7 +1471,7 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>7710</v>
+        <v>7759</v>
       </c>
     </row>
     <row r="13">
@@ -1479,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>97.56999999999999</v>
+        <v>99.66</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -1488,7 +1488,7 @@
         <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>80.83</v>
+        <v>84.8</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -1500,7 +1500,7 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>7619</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="14">
@@ -1508,16 +1508,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>94.42</v>
+        <v>96.27</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>882</v>
+        <v>1470.92</v>
       </c>
       <c r="E14">
-        <v>76</v>
+        <v>80.83</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -1529,7 +1529,7 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>7222</v>
+        <v>7262</v>
       </c>
     </row>
     <row r="15">
@@ -1537,7 +1537,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>96.65000000000001</v>
+        <v>98.53</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1546,7 +1546,7 @@
         <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>80.5</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -1558,7 +1558,7 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>6998</v>
+        <v>7081</v>
       </c>
     </row>
     <row r="16">
@@ -1566,16 +1566,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>96.40000000000001</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
       <c r="D16">
-        <v>758</v>
+        <v>823.72</v>
       </c>
       <c r="E16">
-        <v>78.72</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -1587,7 +1587,7 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>6637</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="17">
@@ -1595,28 +1595,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>95.61</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>912.71</v>
+        <v>870.71</v>
       </c>
       <c r="E17">
-        <v>79.09</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="F17">
         <v>42</v>
       </c>
       <c r="G17">
-        <v>84</v>
+        <v>80.39230000000001</v>
       </c>
       <c r="H17">
         <v>126</v>
       </c>
       <c r="I17">
-        <v>6492</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="18">
@@ -1624,16 +1624,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>94.01000000000001</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>710.39</v>
+        <v>778.98</v>
       </c>
       <c r="E18">
-        <v>74.01000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -1645,7 +1645,7 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>6238</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="19">
@@ -1653,16 +1653,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>95.31</v>
+        <v>97.5</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>929.4</v>
+        <v>1284.08</v>
       </c>
       <c r="E19">
-        <v>80.27</v>
+        <v>85.44</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -1674,7 +1674,7 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>6050</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="20">
@@ -1682,16 +1682,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>95.47</v>
+        <v>97.81</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>736.98</v>
+        <v>1136.64</v>
       </c>
       <c r="E20">
-        <v>79.01000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -1703,7 +1703,7 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>5952</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="21">
@@ -1711,28 +1711,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>93.43000000000001</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="C21">
         <v>6</v>
       </c>
       <c r="D21">
-        <v>798</v>
+        <v>768.04</v>
       </c>
       <c r="E21">
-        <v>76.88</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="F21">
         <v>42</v>
       </c>
       <c r="G21">
-        <v>80.39230000000001</v>
+        <v>73.72</v>
       </c>
       <c r="H21">
         <v>126</v>
       </c>
       <c r="I21">
-        <v>5642</v>
+        <v>5714</v>
       </c>
     </row>
     <row r="22">
@@ -1740,16 +1740,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>96.62</v>
+        <v>98.83</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22">
-        <v>882</v>
+        <v>1004.65</v>
       </c>
       <c r="E22">
-        <v>80.18000000000001</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1761,7 +1761,7 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>5622</v>
+        <v>5685</v>
       </c>
     </row>
     <row r="23">
@@ -1769,28 +1769,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>93.25</v>
+        <v>95.48</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>1028.35</v>
+        <v>840</v>
       </c>
       <c r="E23">
-        <v>75.73</v>
+        <v>80.05</v>
       </c>
       <c r="F23">
         <v>42</v>
       </c>
       <c r="G23">
-        <v>84</v>
+        <v>80.39230000000001</v>
       </c>
       <c r="H23">
         <v>126</v>
       </c>
       <c r="I23">
-        <v>5258</v>
+        <v>5332</v>
       </c>
     </row>
     <row r="24">
@@ -1798,16 +1798,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>95.95999999999999</v>
+        <v>97.73</v>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24">
-        <v>875.47</v>
+        <v>1045.53</v>
       </c>
       <c r="E24">
-        <v>78.06</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1819,7 +1819,7 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>5249</v>
+        <v>5303</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
@@ -407,16 +407,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>120.61</v>
+        <v>131.36</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>1213.1</v>
+        <v>1376.7</v>
       </c>
       <c r="E2">
-        <v>97.98999999999999</v>
+        <v>114.16</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -428,7 +428,7 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>18396</v>
+        <v>18925</v>
       </c>
     </row>
     <row r="3">
@@ -436,16 +436,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>103.62</v>
+        <v>111.56</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>871.26</v>
+        <v>1414.58</v>
       </c>
       <c r="E3">
-        <v>89.90000000000001</v>
+        <v>103.16</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -454,10 +454,10 @@
         <v>84</v>
       </c>
       <c r="H3">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I3">
-        <v>14967</v>
+        <v>15445</v>
       </c>
     </row>
     <row r="4">
@@ -465,16 +465,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>105.66</v>
+        <v>113.08</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4">
-        <v>1078.73</v>
+        <v>1260.44</v>
       </c>
       <c r="E4">
-        <v>90.65000000000001</v>
+        <v>102.41</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -483,10 +483,10 @@
         <v>84</v>
       </c>
       <c r="H4">
-        <v>126</v>
+        <v>143.83</v>
       </c>
       <c r="I4">
-        <v>13635</v>
+        <v>14088</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>98.54000000000001</v>
+        <v>105.06</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -503,7 +503,7 @@
         <v>1735.8</v>
       </c>
       <c r="E5">
-        <v>83.97</v>
+        <v>95.3</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -515,7 +515,7 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>12226</v>
+        <v>12614</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>100.58</v>
+        <v>107.2</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -532,7 +532,7 @@
         <v>1242.08</v>
       </c>
       <c r="E6">
-        <v>86.67</v>
+        <v>98.09</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -544,7 +544,7 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>10968</v>
+        <v>11322</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>98.97</v>
+        <v>105.43</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -561,7 +561,7 @@
         <v>1963.94</v>
       </c>
       <c r="E7">
-        <v>86.56999999999999</v>
+        <v>98.14</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -573,7 +573,7 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>10006</v>
+        <v>10363</v>
       </c>
     </row>
     <row r="8">
@@ -581,16 +581,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>100.11</v>
+        <v>106.82</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1139.72</v>
+        <v>1811.25</v>
       </c>
       <c r="E8">
-        <v>86.48999999999999</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -602,7 +602,7 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>9483</v>
+        <v>9780</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>96.2</v>
+        <v>102.23</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -619,19 +619,19 @@
         <v>1276.66</v>
       </c>
       <c r="E9">
-        <v>81.69</v>
+        <v>91.3</v>
       </c>
       <c r="F9">
         <v>42</v>
       </c>
       <c r="G9">
-        <v>80.39230000000001</v>
+        <v>84</v>
       </c>
       <c r="H9">
         <v>126</v>
       </c>
       <c r="I9">
-        <v>8950</v>
+        <v>9232</v>
       </c>
     </row>
     <row r="10">
@@ -639,16 +639,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>98.51000000000001</v>
+        <v>104.37</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1909.94</v>
+        <v>1405.94</v>
       </c>
       <c r="E10">
-        <v>85.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -660,7 +660,7 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>8646</v>
+        <v>8898</v>
       </c>
     </row>
     <row r="11">
@@ -668,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>97.53</v>
+        <v>103.84</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -677,7 +677,7 @@
         <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>81.09</v>
+        <v>91.05</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -689,7 +689,7 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>8306</v>
+        <v>8566</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +697,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>96.7</v>
+        <v>103.28</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -706,7 +706,7 @@
         <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>81.25</v>
+        <v>92.25</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -718,7 +718,7 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>7877</v>
+        <v>8131</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>99.52</v>
+        <v>106.19</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>85</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -747,7 +747,7 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>7824</v>
+        <v>8056</v>
       </c>
     </row>
     <row r="14">
@@ -755,7 +755,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>96.43000000000001</v>
+        <v>102.93</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -764,7 +764,7 @@
         <v>1470.92</v>
       </c>
       <c r="E14">
-        <v>81.3</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -776,7 +776,7 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>7375</v>
+        <v>7628</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +784,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>98.51000000000001</v>
+        <v>105.11</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -793,7 +793,7 @@
         <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>84.84999999999999</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -805,7 +805,7 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>7187</v>
+        <v>7416</v>
       </c>
     </row>
     <row r="16">
@@ -813,16 +813,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>97.77</v>
+        <v>104.59</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
       <c r="D16">
-        <v>823.72</v>
+        <v>1387</v>
       </c>
       <c r="E16">
-        <v>82.87</v>
+        <v>95.95</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -834,7 +834,7 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>6824</v>
+        <v>7051</v>
       </c>
     </row>
     <row r="17">
@@ -842,28 +842,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>96.92</v>
+        <v>103.62</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>870.71</v>
+        <v>1063.5</v>
       </c>
       <c r="E17">
-        <v>82.56</v>
+        <v>94.72</v>
       </c>
       <c r="F17">
         <v>42</v>
       </c>
       <c r="G17">
-        <v>80.39230000000001</v>
+        <v>84</v>
       </c>
       <c r="H17">
         <v>126</v>
       </c>
       <c r="I17">
-        <v>6696</v>
+        <v>6913</v>
       </c>
     </row>
     <row r="18">
@@ -871,16 +871,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>96.28</v>
+        <v>102.02</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>778.98</v>
+        <v>894.09</v>
       </c>
       <c r="E18">
-        <v>78.79000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -892,7 +892,7 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>6390</v>
+        <v>6599</v>
       </c>
     </row>
     <row r="19">
@@ -900,16 +900,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>97.31999999999999</v>
+        <v>103.93</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>1284.08</v>
+        <v>1355.58</v>
       </c>
       <c r="E19">
-        <v>85.19</v>
+        <v>96.61</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -921,7 +921,7 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>6206</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="20">
@@ -929,16 +929,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>97.7</v>
+        <v>103.32</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>1136.64</v>
+        <v>1135</v>
       </c>
       <c r="E20">
-        <v>83.45</v>
+        <v>92.62</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -950,7 +950,7 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>6099</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="21">
@@ -958,28 +958,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>95.84</v>
+        <v>101.81</v>
       </c>
       <c r="C21">
         <v>6</v>
       </c>
       <c r="D21">
-        <v>768.04</v>
+        <v>893.2</v>
       </c>
       <c r="E21">
-        <v>80.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F21">
         <v>42</v>
       </c>
       <c r="G21">
-        <v>76.7846</v>
+        <v>84</v>
       </c>
       <c r="H21">
         <v>126</v>
       </c>
       <c r="I21">
-        <v>5791</v>
+        <v>5955</v>
       </c>
     </row>
     <row r="22">
@@ -987,16 +987,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>98.87</v>
+        <v>105.88</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22">
-        <v>1004.65</v>
+        <v>1462.46</v>
       </c>
       <c r="E22">
-        <v>85.77</v>
+        <v>98.75</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1008,7 +1008,7 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>5764</v>
+        <v>5929</v>
       </c>
     </row>
     <row r="23">
@@ -1016,28 +1016,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>95.41</v>
+        <v>102.2</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>840</v>
+        <v>1457.35</v>
       </c>
       <c r="E23">
-        <v>79.95</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="F23">
         <v>42</v>
       </c>
       <c r="G23">
-        <v>80.39230000000001</v>
+        <v>84</v>
       </c>
       <c r="H23">
         <v>126</v>
       </c>
       <c r="I23">
-        <v>5406</v>
+        <v>5565</v>
       </c>
     </row>
     <row r="24">
@@ -1045,16 +1045,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>97.69</v>
+        <v>104.28</v>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24">
-        <v>1045.53</v>
+        <v>1299.29</v>
       </c>
       <c r="E24">
-        <v>81.98</v>
+        <v>92.48</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1066,7 +1066,7 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>5358</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="25">
@@ -1074,16 +1074,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>95.09</v>
+        <v>102.51</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25">
-        <v>775.2</v>
+        <v>817.2</v>
       </c>
       <c r="E25">
-        <v>79.08</v>
+        <v>91.91</v>
       </c>
       <c r="F25">
         <v>42</v>
@@ -1095,7 +1095,7 @@
         <v>126</v>
       </c>
       <c r="I25">
-        <v>4954</v>
+        <v>5110</v>
       </c>
     </row>
   </sheetData>
@@ -1160,16 +1160,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>120.61</v>
+        <v>131.36</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>1213.1</v>
+        <v>1376.7</v>
       </c>
       <c r="E2">
-        <v>97.98999999999999</v>
+        <v>114.16</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -1181,7 +1181,7 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>18396</v>
+        <v>18925</v>
       </c>
     </row>
     <row r="3">
@@ -1189,16 +1189,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>103.8</v>
+        <v>111.76</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>871.26</v>
+        <v>1414.58</v>
       </c>
       <c r="E3">
-        <v>89.79000000000001</v>
+        <v>103.19</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -1207,10 +1207,10 @@
         <v>84</v>
       </c>
       <c r="H3">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I3">
-        <v>14651</v>
+        <v>15122</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>105.64</v>
+        <v>113.09</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4">
-        <v>1078.73</v>
+        <v>1260.44</v>
       </c>
       <c r="E4">
-        <v>90.47</v>
+        <v>102.35</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -1236,10 +1236,10 @@
         <v>84</v>
       </c>
       <c r="H4">
-        <v>126</v>
+        <v>141.59</v>
       </c>
       <c r="I4">
-        <v>13352</v>
+        <v>13797</v>
       </c>
     </row>
     <row r="5">
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>100.57</v>
+        <v>107.45</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1256,7 +1256,7 @@
         <v>1735.8</v>
       </c>
       <c r="E5">
-        <v>85.01000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -1268,7 +1268,7 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>11304</v>
+        <v>11630</v>
       </c>
     </row>
     <row r="6">
@@ -1276,7 +1276,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>101.44</v>
+        <v>108.15</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1285,7 +1285,7 @@
         <v>1242.08</v>
       </c>
       <c r="E6">
-        <v>86.98999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -1297,7 +1297,7 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>10493</v>
+        <v>10819</v>
       </c>
     </row>
     <row r="7">
@@ -1305,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>99.45</v>
+        <v>105.96</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1314,7 +1314,7 @@
         <v>1963.94</v>
       </c>
       <c r="E7">
-        <v>86.95999999999999</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -1326,7 +1326,7 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>9694</v>
+        <v>10035</v>
       </c>
     </row>
     <row r="8">
@@ -1334,16 +1334,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>100.3</v>
+        <v>107.04</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1139.72</v>
+        <v>1811.25</v>
       </c>
       <c r="E8">
-        <v>86.68000000000001</v>
+        <v>99.64</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -1355,7 +1355,7 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>9248</v>
+        <v>9539</v>
       </c>
     </row>
     <row r="9">
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>96.25</v>
+        <v>102.26</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1372,19 +1372,19 @@
         <v>1276.66</v>
       </c>
       <c r="E9">
-        <v>81.81999999999999</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="F9">
         <v>42</v>
       </c>
       <c r="G9">
-        <v>80.39230000000001</v>
+        <v>84</v>
       </c>
       <c r="H9">
         <v>126</v>
       </c>
       <c r="I9">
-        <v>8750</v>
+        <v>9022</v>
       </c>
     </row>
     <row r="10">
@@ -1392,16 +1392,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>98.59999999999999</v>
+        <v>104.49</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1909.94</v>
+        <v>1405.94</v>
       </c>
       <c r="E10">
-        <v>85.25</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -1413,7 +1413,7 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>8476</v>
+        <v>8723</v>
       </c>
     </row>
     <row r="11">
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>97.81999999999999</v>
+        <v>104.22</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1430,7 +1430,7 @@
         <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>81.19</v>
+        <v>91.28</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -1442,7 +1442,7 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>8152</v>
+        <v>8405</v>
       </c>
     </row>
     <row r="12">
@@ -1450,7 +1450,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>96.88</v>
+        <v>103.41</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1459,7 +1459,7 @@
         <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>81.38</v>
+        <v>92.34</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -1471,7 +1471,7 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>7759</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="13">
@@ -1479,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>99.66</v>
+        <v>106.25</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -1488,7 +1488,7 @@
         <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>84.8</v>
+        <v>94.92</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -1500,7 +1500,7 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>7669</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="14">
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>96.27</v>
+        <v>102.66</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1517,7 +1517,7 @@
         <v>1470.92</v>
       </c>
       <c r="E14">
-        <v>80.83</v>
+        <v>89.89</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -1529,7 +1529,7 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>7262</v>
+        <v>7512</v>
       </c>
     </row>
     <row r="15">
@@ -1537,7 +1537,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>98.53</v>
+        <v>105.13</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1546,7 +1546,7 @@
         <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>84.79000000000001</v>
+        <v>97.42</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -1558,7 +1558,7 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>7081</v>
+        <v>7308</v>
       </c>
     </row>
     <row r="16">
@@ -1566,16 +1566,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>97.73999999999999</v>
+        <v>104.6</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
       <c r="D16">
-        <v>823.72</v>
+        <v>1387</v>
       </c>
       <c r="E16">
-        <v>82.90000000000001</v>
+        <v>96.13</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -1587,7 +1587,7 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>6720</v>
+        <v>6943</v>
       </c>
     </row>
     <row r="17">
@@ -1595,28 +1595,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>97.01000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>870.71</v>
+        <v>1063.5</v>
       </c>
       <c r="E17">
-        <v>82.56999999999999</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="F17">
         <v>42</v>
       </c>
       <c r="G17">
-        <v>80.39230000000001</v>
+        <v>84</v>
       </c>
       <c r="H17">
         <v>126</v>
       </c>
       <c r="I17">
-        <v>6592</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="18">
@@ -1624,16 +1624,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>96.18000000000001</v>
+        <v>101.93</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>778.98</v>
+        <v>894.09</v>
       </c>
       <c r="E18">
-        <v>78.45</v>
+        <v>87.52</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -1645,7 +1645,7 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>6301</v>
+        <v>6508</v>
       </c>
     </row>
     <row r="19">
@@ -1653,16 +1653,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>97.5</v>
+        <v>104.21</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>1284.08</v>
+        <v>1355.58</v>
       </c>
       <c r="E19">
-        <v>85.44</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -1674,7 +1674,7 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>6119</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="20">
@@ -1682,16 +1682,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>97.81</v>
+        <v>103.38</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>1136.64</v>
+        <v>1135</v>
       </c>
       <c r="E20">
-        <v>83.48</v>
+        <v>92.52</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -1703,7 +1703,7 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>6028</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="21">
@@ -1711,28 +1711,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>95.48999999999999</v>
+        <v>101.43</v>
       </c>
       <c r="C21">
         <v>6</v>
       </c>
       <c r="D21">
-        <v>768.04</v>
+        <v>893.2</v>
       </c>
       <c r="E21">
-        <v>79.98999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F21">
         <v>42</v>
       </c>
       <c r="G21">
-        <v>73.72</v>
+        <v>84</v>
       </c>
       <c r="H21">
         <v>126</v>
       </c>
       <c r="I21">
-        <v>5714</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="22">
@@ -1740,16 +1740,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>98.83</v>
+        <v>105.77</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22">
-        <v>1004.65</v>
+        <v>1462.46</v>
       </c>
       <c r="E22">
-        <v>85.79000000000001</v>
+        <v>98.62</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1761,7 +1761,7 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>5685</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="23">
@@ -1769,28 +1769,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>95.48</v>
+        <v>102.31</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>840</v>
+        <v>1457.35</v>
       </c>
       <c r="E23">
-        <v>80.05</v>
+        <v>93</v>
       </c>
       <c r="F23">
         <v>42</v>
       </c>
       <c r="G23">
-        <v>80.39230000000001</v>
+        <v>84</v>
       </c>
       <c r="H23">
         <v>126</v>
       </c>
       <c r="I23">
-        <v>5332</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="24">
@@ -1798,16 +1798,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>97.73</v>
+        <v>104.33</v>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24">
-        <v>1045.53</v>
+        <v>1299.29</v>
       </c>
       <c r="E24">
-        <v>81.93000000000001</v>
+        <v>92.52</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1819,7 +1819,7 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>5303</v>
+        <v>5468</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,7 +398,22 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>n_pts</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
@@ -407,28 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>131.36</v>
+        <v>95.14</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1376.7</v>
+        <v>882</v>
       </c>
       <c r="E2">
-        <v>114.16</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>38.39</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>73.72</v>
       </c>
       <c r="H2">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="I2">
-        <v>18925</v>
+        <v>16978</v>
+      </c>
+      <c r="J2">
+        <v>0.76</v>
+      </c>
+      <c r="K2">
+        <v>93.64</v>
+      </c>
+      <c r="L2">
+        <v>96.63</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>111.56</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1414.58</v>
+        <v>877.74</v>
       </c>
       <c r="E3">
-        <v>103.16</v>
+        <v>85.16</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G3">
+        <v>42</v>
+      </c>
+      <c r="H3">
         <v>84</v>
       </c>
-      <c r="H3">
-        <v>132</v>
-      </c>
       <c r="I3">
-        <v>15445</v>
+        <v>16978</v>
+      </c>
+      <c r="J3">
+        <v>0.65</v>
+      </c>
+      <c r="K3">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="L3">
+        <v>66.77</v>
       </c>
     </row>
     <row r="4">
@@ -465,28 +498,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>113.08</v>
+        <v>56.64</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1260.44</v>
+        <v>1008</v>
       </c>
       <c r="E4">
-        <v>102.41</v>
+        <v>84.63</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>31.72</v>
+      </c>
+      <c r="H4">
         <v>84</v>
       </c>
-      <c r="H4">
-        <v>143.83</v>
-      </c>
       <c r="I4">
-        <v>14088</v>
+        <v>16978</v>
+      </c>
+      <c r="J4">
+        <v>0.65</v>
+      </c>
+      <c r="K4">
+        <v>55.37</v>
+      </c>
+      <c r="L4">
+        <v>57.92</v>
       </c>
     </row>
     <row r="5">
@@ -494,28 +536,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>105.06</v>
+        <v>47.41</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1735.8</v>
+        <v>1182.9</v>
       </c>
       <c r="E5">
-        <v>95.3</v>
+        <v>76.72</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>126</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="I5">
-        <v>12614</v>
+        <v>16978</v>
+      </c>
+      <c r="J5">
+        <v>0.59</v>
+      </c>
+      <c r="K5">
+        <v>46.26</v>
+      </c>
+      <c r="L5">
+        <v>48.56</v>
       </c>
     </row>
     <row r="6">
@@ -523,28 +574,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>107.2</v>
+        <v>44.94</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1242.08</v>
+        <v>905.96</v>
       </c>
       <c r="E6">
-        <v>98.09</v>
+        <v>77.3</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I6">
-        <v>11322</v>
+        <v>16978</v>
+      </c>
+      <c r="J6">
+        <v>0.59</v>
+      </c>
+      <c r="K6">
+        <v>43.78</v>
+      </c>
+      <c r="L6">
+        <v>46.11</v>
       </c>
     </row>
     <row r="7">
@@ -552,28 +612,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>105.43</v>
+        <v>41.16</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1963.94</v>
+        <v>841.54</v>
       </c>
       <c r="E7">
-        <v>98.14</v>
+        <v>73.83</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>10363</v>
+        <v>16978</v>
+      </c>
+      <c r="J7">
+        <v>0.57</v>
+      </c>
+      <c r="K7">
+        <v>40.05</v>
+      </c>
+      <c r="L7">
+        <v>42.27</v>
       </c>
     </row>
     <row r="8">
@@ -581,28 +650,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>106.82</v>
+        <v>39.48</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1811.25</v>
+        <v>1166.09</v>
       </c>
       <c r="E8">
-        <v>99.23999999999999</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>9780</v>
+        <v>16978</v>
+      </c>
+      <c r="J8">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K8">
+        <v>38.38</v>
+      </c>
+      <c r="L8">
+        <v>40.58</v>
       </c>
     </row>
     <row r="9">
@@ -610,28 +688,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>102.23</v>
+        <v>35.79</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1276.66</v>
+        <v>817.2</v>
       </c>
       <c r="E9">
-        <v>91.3</v>
+        <v>68.63</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>9232</v>
+        <v>16978</v>
+      </c>
+      <c r="J9">
+        <v>0.53</v>
+      </c>
+      <c r="K9">
+        <v>34.76</v>
+      </c>
+      <c r="L9">
+        <v>36.82</v>
       </c>
     </row>
     <row r="10">
@@ -639,28 +726,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>104.37</v>
+        <v>35.62</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1405.94</v>
+        <v>756</v>
       </c>
       <c r="E10">
-        <v>94.2</v>
+        <v>69.56</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>8898</v>
+        <v>16978</v>
+      </c>
+      <c r="J10">
+        <v>0.53</v>
+      </c>
+      <c r="K10">
+        <v>34.57</v>
+      </c>
+      <c r="L10">
+        <v>36.67</v>
       </c>
     </row>
     <row r="11">
@@ -668,28 +764,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>103.84</v>
+        <v>34.14</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1466.24</v>
+        <v>741.5700000000001</v>
       </c>
       <c r="E11">
-        <v>91.05</v>
+        <v>67.33</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>8566</v>
+        <v>16978</v>
+      </c>
+      <c r="J11">
+        <v>0.52</v>
+      </c>
+      <c r="K11">
+        <v>33.12</v>
+      </c>
+      <c r="L11">
+        <v>35.15</v>
       </c>
     </row>
     <row r="12">
@@ -697,28 +802,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>103.28</v>
+        <v>32.3</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1580.75</v>
+        <v>1169.74</v>
       </c>
       <c r="E12">
-        <v>92.25</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>8131</v>
+        <v>16978</v>
+      </c>
+      <c r="J12">
+        <v>0.51</v>
+      </c>
+      <c r="K12">
+        <v>31.3</v>
+      </c>
+      <c r="L12">
+        <v>33.29</v>
       </c>
     </row>
     <row r="13">
@@ -726,28 +840,37 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>106.19</v>
+        <v>32.8</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1324.98</v>
+        <v>1072.32</v>
       </c>
       <c r="E13">
-        <v>95.18000000000001</v>
+        <v>67.87</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I13">
-        <v>8056</v>
+        <v>16978</v>
+      </c>
+      <c r="J13">
+        <v>0.52</v>
+      </c>
+      <c r="K13">
+        <v>31.78</v>
+      </c>
+      <c r="L13">
+        <v>33.82</v>
       </c>
     </row>
     <row r="14">
@@ -755,28 +878,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>102.93</v>
+        <v>30.38</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1470.92</v>
+        <v>705.48</v>
       </c>
       <c r="E14">
-        <v>90.56999999999999</v>
+        <v>63.94</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>7628</v>
+        <v>16978</v>
+      </c>
+      <c r="J14">
+        <v>0.49</v>
+      </c>
+      <c r="K14">
+        <v>29.42</v>
+      </c>
+      <c r="L14">
+        <v>31.34</v>
       </c>
     </row>
     <row r="15">
@@ -784,28 +916,37 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>105.11</v>
+        <v>29.79</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1391.3</v>
+        <v>754.67</v>
       </c>
       <c r="E15">
-        <v>97.48999999999999</v>
+        <v>64.77</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>7416</v>
+        <v>16978</v>
+      </c>
+      <c r="J15">
+        <v>0.5</v>
+      </c>
+      <c r="K15">
+        <v>28.82</v>
+      </c>
+      <c r="L15">
+        <v>30.77</v>
       </c>
     </row>
     <row r="16">
@@ -813,28 +954,37 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>104.59</v>
+        <v>28.22</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1387</v>
+        <v>855.15</v>
       </c>
       <c r="E16">
-        <v>95.95</v>
+        <v>63.84</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I16">
-        <v>7051</v>
+        <v>16978</v>
+      </c>
+      <c r="J16">
+        <v>0.49</v>
+      </c>
+      <c r="K16">
+        <v>27.26</v>
+      </c>
+      <c r="L16">
+        <v>29.18</v>
       </c>
     </row>
     <row r="17">
@@ -842,28 +992,37 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>103.62</v>
+        <v>27.59</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1063.5</v>
+        <v>754.2</v>
       </c>
       <c r="E17">
-        <v>94.72</v>
+        <v>62.59</v>
       </c>
       <c r="F17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I17">
-        <v>6913</v>
+        <v>16978</v>
+      </c>
+      <c r="J17">
+        <v>0.48</v>
+      </c>
+      <c r="K17">
+        <v>26.65</v>
+      </c>
+      <c r="L17">
+        <v>28.53</v>
       </c>
     </row>
     <row r="18">
@@ -871,28 +1030,37 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>102.02</v>
+        <v>26.05</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>894.09</v>
+        <v>588</v>
       </c>
       <c r="E18">
-        <v>87.78</v>
+        <v>58.89</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>126</v>
+        <v>31.72</v>
       </c>
       <c r="I18">
-        <v>6599</v>
+        <v>16978</v>
+      </c>
+      <c r="J18">
+        <v>0.45</v>
+      </c>
+      <c r="K18">
+        <v>25.16</v>
+      </c>
+      <c r="L18">
+        <v>26.93</v>
       </c>
     </row>
     <row r="19">
@@ -900,28 +1068,37 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>103.93</v>
+        <v>26.03</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1355.58</v>
+        <v>863.6799999999999</v>
       </c>
       <c r="E19">
-        <v>96.61</v>
+        <v>61.57</v>
       </c>
       <c r="F19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>126</v>
+        <v>19.2</v>
       </c>
       <c r="I19">
-        <v>6429</v>
+        <v>16978</v>
+      </c>
+      <c r="J19">
+        <v>0.47</v>
+      </c>
+      <c r="K19">
+        <v>25.1</v>
+      </c>
+      <c r="L19">
+        <v>26.95</v>
       </c>
     </row>
     <row r="20">
@@ -929,28 +1106,37 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>103.32</v>
+        <v>24.96</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1135</v>
+        <v>740.58</v>
       </c>
       <c r="E20">
-        <v>92.62</v>
+        <v>59.63</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>6278</v>
+        <v>16978</v>
+      </c>
+      <c r="J20">
+        <v>0.46</v>
+      </c>
+      <c r="K20">
+        <v>24.06</v>
+      </c>
+      <c r="L20">
+        <v>25.86</v>
       </c>
     </row>
     <row r="21">
@@ -958,28 +1144,37 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>101.81</v>
+        <v>23.16</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>893.2</v>
+        <v>763.54</v>
       </c>
       <c r="E21">
-        <v>90.90000000000001</v>
+        <v>56.95</v>
       </c>
       <c r="F21">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>5955</v>
+        <v>16978</v>
+      </c>
+      <c r="J21">
+        <v>0.44</v>
+      </c>
+      <c r="K21">
+        <v>22.31</v>
+      </c>
+      <c r="L21">
+        <v>24.02</v>
       </c>
     </row>
     <row r="22">
@@ -987,28 +1182,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>105.88</v>
+        <v>24.14</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1462.46</v>
+        <v>882</v>
       </c>
       <c r="E22">
-        <v>98.75</v>
+        <v>60.2</v>
       </c>
       <c r="F22">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>5929</v>
+        <v>16978</v>
+      </c>
+      <c r="J22">
+        <v>0.46</v>
+      </c>
+      <c r="K22">
+        <v>23.23</v>
+      </c>
+      <c r="L22">
+        <v>25.04</v>
       </c>
     </row>
     <row r="23">
@@ -1016,28 +1220,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>102.2</v>
+        <v>21.85</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1457.35</v>
+        <v>840</v>
       </c>
       <c r="E23">
-        <v>92.81999999999999</v>
+        <v>56.05</v>
       </c>
       <c r="F23">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>5565</v>
+        <v>16978</v>
+      </c>
+      <c r="J23">
+        <v>0.43</v>
+      </c>
+      <c r="K23">
+        <v>21.01</v>
+      </c>
+      <c r="L23">
+        <v>22.69</v>
       </c>
     </row>
     <row r="24">
@@ -1045,28 +1258,37 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>104.28</v>
+        <v>22.09</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1299.29</v>
+        <v>715.7</v>
       </c>
       <c r="E24">
-        <v>92.48</v>
+        <v>57.02</v>
       </c>
       <c r="F24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>5525</v>
+        <v>16978</v>
+      </c>
+      <c r="J24">
+        <v>0.44</v>
+      </c>
+      <c r="K24">
+        <v>21.23</v>
+      </c>
+      <c r="L24">
+        <v>22.95</v>
       </c>
     </row>
     <row r="25">
@@ -1074,28 +1296,37 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>102.51</v>
+        <v>20.12</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>817.2</v>
+        <v>824.58</v>
       </c>
       <c r="E25">
-        <v>91.91</v>
+        <v>54.13</v>
       </c>
       <c r="F25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>5110</v>
+        <v>16978</v>
+      </c>
+      <c r="J25">
+        <v>0.42</v>
+      </c>
+      <c r="K25">
+        <v>19.31</v>
+      </c>
+      <c r="L25">
+        <v>20.94</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1116,42 +1347,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_cost</t>
+          <t>mean_costs</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>min_cost</t>
+          <t>min_costs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>max_cost</t>
+          <t>max_costs</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sd_cost</t>
+          <t>sd_costs</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q1_cost</t>
+          <t>q1_costs</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>median_cost</t>
+          <t>median_costs</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q3_cost</t>
+          <t>q3_costs</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>n_pts</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
@@ -1160,28 +1406,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>131.36</v>
+        <v>96.34</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1376.7</v>
+        <v>882</v>
       </c>
       <c r="E2">
-        <v>114.16</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>31.72</v>
       </c>
       <c r="G2">
+        <v>42</v>
+      </c>
+      <c r="H2">
         <v>84</v>
       </c>
-      <c r="H2">
-        <v>168</v>
-      </c>
       <c r="I2">
-        <v>18925</v>
+        <v>16978</v>
+      </c>
+      <c r="J2">
+        <v>0.58</v>
+      </c>
+      <c r="K2">
+        <v>95.2</v>
+      </c>
+      <c r="L2">
+        <v>97.48</v>
       </c>
     </row>
     <row r="3">
@@ -1189,28 +1444,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>111.76</v>
+        <v>68.59</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1414.58</v>
+        <v>798</v>
       </c>
       <c r="E3">
-        <v>103.19</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G3">
+        <v>42</v>
+      </c>
+      <c r="H3">
         <v>84</v>
       </c>
-      <c r="H3">
-        <v>132</v>
-      </c>
       <c r="I3">
-        <v>15122</v>
+        <v>15934</v>
+      </c>
+      <c r="J3">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K3">
+        <v>67.5</v>
+      </c>
+      <c r="L3">
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1218,28 +1482,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>113.09</v>
+        <v>65.52</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1260.44</v>
+        <v>1008</v>
       </c>
       <c r="E4">
-        <v>102.35</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>42</v>
+      </c>
+      <c r="H4">
         <v>84</v>
       </c>
-      <c r="H4">
-        <v>141.59</v>
-      </c>
       <c r="I4">
-        <v>13797</v>
+        <v>14690</v>
+      </c>
+      <c r="J4">
+        <v>0.59</v>
+      </c>
+      <c r="K4">
+        <v>64.37</v>
+      </c>
+      <c r="L4">
+        <v>66.67</v>
       </c>
     </row>
     <row r="5">
@@ -1247,28 +1520,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>107.45</v>
+        <v>57.56</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1735.8</v>
+        <v>741.86</v>
       </c>
       <c r="E5">
-        <v>96.68000000000001</v>
+        <v>65.12</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>84</v>
+        <v>38.39</v>
       </c>
       <c r="H5">
-        <v>126</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="I5">
-        <v>11630</v>
+        <v>14067</v>
+      </c>
+      <c r="J5">
+        <v>0.55</v>
+      </c>
+      <c r="K5">
+        <v>56.49</v>
+      </c>
+      <c r="L5">
+        <v>58.64</v>
       </c>
     </row>
     <row r="6">
@@ -1276,28 +1558,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>108.15</v>
+        <v>56.17</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1242.08</v>
+        <v>714</v>
       </c>
       <c r="E6">
-        <v>98.2</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>84</v>
+        <v>36.86</v>
       </c>
       <c r="H6">
-        <v>126</v>
+        <v>63.44</v>
       </c>
       <c r="I6">
-        <v>10819</v>
+        <v>13705</v>
+      </c>
+      <c r="J6">
+        <v>0.58</v>
+      </c>
+      <c r="K6">
+        <v>55.04</v>
+      </c>
+      <c r="L6">
+        <v>57.3</v>
       </c>
     </row>
     <row r="7">
@@ -1305,28 +1596,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>105.96</v>
+        <v>52.69</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1963.94</v>
+        <v>840</v>
       </c>
       <c r="E7">
-        <v>98.48999999999999</v>
+        <v>64.78</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>84</v>
+        <v>31.72</v>
       </c>
       <c r="H7">
-        <v>126</v>
+        <v>53.49</v>
       </c>
       <c r="I7">
-        <v>10035</v>
+        <v>13405</v>
+      </c>
+      <c r="J7">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K7">
+        <v>51.6</v>
+      </c>
+      <c r="L7">
+        <v>53.79</v>
       </c>
     </row>
     <row r="8">
@@ -1334,28 +1634,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>107.04</v>
+        <v>51.52</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1811.25</v>
+        <v>756</v>
       </c>
       <c r="E8">
-        <v>99.64</v>
+        <v>64.58</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>84</v>
+        <v>26.75</v>
       </c>
       <c r="H8">
-        <v>126</v>
+        <v>49.38</v>
       </c>
       <c r="I8">
-        <v>9539</v>
+        <v>13143</v>
+      </c>
+      <c r="J8">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K8">
+        <v>50.41</v>
+      </c>
+      <c r="L8">
+        <v>52.62</v>
       </c>
     </row>
     <row r="9">
@@ -1363,28 +1672,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>102.26</v>
+        <v>47.48</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1276.66</v>
+        <v>798</v>
       </c>
       <c r="E9">
-        <v>91.31999999999999</v>
+        <v>62.92</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>84</v>
+        <v>19.2</v>
       </c>
       <c r="H9">
-        <v>126</v>
+        <v>49.38</v>
       </c>
       <c r="I9">
-        <v>9022</v>
+        <v>12915</v>
+      </c>
+      <c r="J9">
+        <v>0.55</v>
+      </c>
+      <c r="K9">
+        <v>46.39</v>
+      </c>
+      <c r="L9">
+        <v>48.56</v>
       </c>
     </row>
     <row r="10">
@@ -1392,28 +1710,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>104.49</v>
+        <v>48</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1405.94</v>
+        <v>756</v>
       </c>
       <c r="E10">
-        <v>94.43000000000001</v>
+        <v>62.87</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>19.2</v>
       </c>
       <c r="H10">
-        <v>126</v>
+        <v>49.38</v>
       </c>
       <c r="I10">
-        <v>8723</v>
+        <v>12726</v>
+      </c>
+      <c r="J10">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K10">
+        <v>46.9</v>
+      </c>
+      <c r="L10">
+        <v>49.09</v>
       </c>
     </row>
     <row r="11">
@@ -1421,28 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>104.22</v>
+        <v>46.45</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1466.24</v>
+        <v>714</v>
       </c>
       <c r="E11">
-        <v>91.28</v>
+        <v>61.57</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>84</v>
+        <v>19.2</v>
       </c>
       <c r="H11">
-        <v>126</v>
+        <v>49.38</v>
       </c>
       <c r="I11">
-        <v>8405</v>
+        <v>12555</v>
+      </c>
+      <c r="J11">
+        <v>0.55</v>
+      </c>
+      <c r="K11">
+        <v>45.37</v>
+      </c>
+      <c r="L11">
+        <v>47.52</v>
       </c>
     </row>
     <row r="12">
@@ -1450,28 +1786,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>103.41</v>
+        <v>44.63</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1580.75</v>
+        <v>588</v>
       </c>
       <c r="E12">
-        <v>92.34</v>
+        <v>60.56</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="H12">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>8011</v>
+        <v>12414</v>
+      </c>
+      <c r="J12">
+        <v>0.54</v>
+      </c>
+      <c r="K12">
+        <v>43.57</v>
+      </c>
+      <c r="L12">
+        <v>45.7</v>
       </c>
     </row>
     <row r="13">
@@ -1479,28 +1824,37 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>106.25</v>
+        <v>45.89</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1324.98</v>
+        <v>882</v>
       </c>
       <c r="E13">
-        <v>94.92</v>
+        <v>62.92</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="H13">
-        <v>126</v>
+        <v>49.38</v>
       </c>
       <c r="I13">
-        <v>7897</v>
+        <v>12275</v>
+      </c>
+      <c r="J13">
+        <v>0.57</v>
+      </c>
+      <c r="K13">
+        <v>44.77</v>
+      </c>
+      <c r="L13">
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -1508,28 +1862,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>102.66</v>
+        <v>43.1</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1470.92</v>
+        <v>630</v>
       </c>
       <c r="E14">
-        <v>89.89</v>
+        <v>60.14</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>7512</v>
+        <v>12101</v>
+      </c>
+      <c r="J14">
+        <v>0.55</v>
+      </c>
+      <c r="K14">
+        <v>42.03</v>
+      </c>
+      <c r="L14">
+        <v>44.17</v>
       </c>
     </row>
     <row r="15">
@@ -1537,28 +1900,37 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>105.13</v>
+        <v>42.76</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1391.3</v>
+        <v>714</v>
       </c>
       <c r="E15">
-        <v>97.42</v>
+        <v>60.96</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>7308</v>
+        <v>11975</v>
+      </c>
+      <c r="J15">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K15">
+        <v>41.67</v>
+      </c>
+      <c r="L15">
+        <v>43.85</v>
       </c>
     </row>
     <row r="16">
@@ -1566,28 +1938,37 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>104.6</v>
+        <v>40.89</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1387</v>
+        <v>672</v>
       </c>
       <c r="E16">
-        <v>96.13</v>
+        <v>60.11</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I16">
-        <v>6943</v>
+        <v>11843</v>
+      </c>
+      <c r="J16">
+        <v>0.55</v>
+      </c>
+      <c r="K16">
+        <v>39.81</v>
+      </c>
+      <c r="L16">
+        <v>41.97</v>
       </c>
     </row>
     <row r="17">
@@ -1595,28 +1976,37 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>103.75</v>
+        <v>40.25</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1063.5</v>
+        <v>588</v>
       </c>
       <c r="E17">
-        <v>94.84999999999999</v>
+        <v>60.08</v>
       </c>
       <c r="F17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I17">
-        <v>6807</v>
+        <v>11724</v>
+      </c>
+      <c r="J17">
+        <v>0.55</v>
+      </c>
+      <c r="K17">
+        <v>39.17</v>
+      </c>
+      <c r="L17">
+        <v>41.34</v>
       </c>
     </row>
     <row r="18">
@@ -1624,28 +2014,37 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>101.93</v>
+        <v>38.51</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>894.09</v>
+        <v>678.4400000000001</v>
       </c>
       <c r="E18">
-        <v>87.52</v>
+        <v>57.61</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I18">
-        <v>6508</v>
+        <v>11598</v>
+      </c>
+      <c r="J18">
+        <v>0.53</v>
+      </c>
+      <c r="K18">
+        <v>37.46</v>
+      </c>
+      <c r="L18">
+        <v>39.55</v>
       </c>
     </row>
     <row r="19">
@@ -1653,28 +2052,37 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>104.21</v>
+        <v>38.95</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1355.58</v>
+        <v>672</v>
       </c>
       <c r="E19">
-        <v>96.95999999999999</v>
+        <v>59.44</v>
       </c>
       <c r="F19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I19">
-        <v>6334</v>
+        <v>11478</v>
+      </c>
+      <c r="J19">
+        <v>0.55</v>
+      </c>
+      <c r="K19">
+        <v>37.86</v>
+      </c>
+      <c r="L19">
+        <v>40.04</v>
       </c>
     </row>
     <row r="20">
@@ -1682,28 +2090,37 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>103.38</v>
+        <v>37.6</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1135</v>
+        <v>588</v>
       </c>
       <c r="E20">
-        <v>92.52</v>
+        <v>58.51</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I20">
-        <v>6204</v>
+        <v>11364</v>
+      </c>
+      <c r="J20">
+        <v>0.55</v>
+      </c>
+      <c r="K20">
+        <v>36.53</v>
+      </c>
+      <c r="L20">
+        <v>38.68</v>
       </c>
     </row>
     <row r="21">
@@ -1711,28 +2128,37 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>101.43</v>
+        <v>35.34</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>893.2</v>
+        <v>630</v>
       </c>
       <c r="E21">
-        <v>90.51000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="F21">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I21">
-        <v>5875</v>
+        <v>11251</v>
+      </c>
+      <c r="J21">
+        <v>0.53</v>
+      </c>
+      <c r="K21">
+        <v>34.31</v>
+      </c>
+      <c r="L21">
+        <v>36.37</v>
       </c>
     </row>
     <row r="22">
@@ -1740,28 +2166,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>105.77</v>
+        <v>37.23</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1462.46</v>
+        <v>756</v>
       </c>
       <c r="E22">
-        <v>98.62</v>
+        <v>59.31</v>
       </c>
       <c r="F22">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I22">
-        <v>5847</v>
+        <v>11131</v>
+      </c>
+      <c r="J22">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K22">
+        <v>36.13</v>
+      </c>
+      <c r="L22">
+        <v>38.33</v>
       </c>
     </row>
     <row r="23">
@@ -1769,28 +2204,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>102.31</v>
+        <v>34.02</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1457.35</v>
+        <v>630</v>
       </c>
       <c r="E23">
-        <v>93</v>
+        <v>55.77</v>
       </c>
       <c r="F23">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I23">
-        <v>5490</v>
+        <v>10994</v>
+      </c>
+      <c r="J23">
+        <v>0.53</v>
+      </c>
+      <c r="K23">
+        <v>32.97</v>
+      </c>
+      <c r="L23">
+        <v>35.06</v>
       </c>
     </row>
     <row r="24">
@@ -1798,28 +2242,75 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>104.33</v>
+        <v>34.8</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1299.29</v>
+        <v>714</v>
       </c>
       <c r="E24">
-        <v>92.52</v>
+        <v>57</v>
       </c>
       <c r="F24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I24">
-        <v>5468</v>
+        <v>10883</v>
+      </c>
+      <c r="J24">
+        <v>0.55</v>
+      </c>
+      <c r="K24">
+        <v>33.73</v>
+      </c>
+      <c r="L24">
+        <v>35.87</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>32.6</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>770.17</v>
+      </c>
+      <c r="E25">
+        <v>55.47</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>42.79</v>
+      </c>
+      <c r="I25">
+        <v>10763</v>
+      </c>
+      <c r="J25">
+        <v>0.53</v>
+      </c>
+      <c r="K25">
+        <v>31.55</v>
+      </c>
+      <c r="L25">
+        <v>33.64</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>95.14</v>
+        <v>101.82</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>882</v>
+        <v>1054.79</v>
       </c>
       <c r="E2">
-        <v>99.43000000000001</v>
+        <v>102.33</v>
       </c>
       <c r="F2">
-        <v>38.39</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>73.72</v>
+        <v>84</v>
       </c>
       <c r="H2">
-        <v>126</v>
+        <v>141.59</v>
       </c>
       <c r="I2">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J2">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K2">
-        <v>93.64</v>
+        <v>100.48</v>
       </c>
       <c r="L2">
-        <v>96.63</v>
+        <v>103.16</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>65.48999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,7 +469,7 @@
         <v>877.74</v>
       </c>
       <c r="E3">
-        <v>85.16</v>
+        <v>89.72</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -478,19 +478,19 @@
         <v>42</v>
       </c>
       <c r="H3">
-        <v>84</v>
+        <v>103.2</v>
       </c>
       <c r="I3">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J3">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="K3">
-        <v>64.20999999999999</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L3">
-        <v>66.77</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -498,37 +498,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>56.64</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1008</v>
+        <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>84.63</v>
+        <v>89.09</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>31.72</v>
+        <v>42</v>
       </c>
       <c r="H4">
         <v>84</v>
       </c>
       <c r="I4">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J4">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="K4">
-        <v>55.37</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="L4">
-        <v>57.92</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>47.41</v>
+        <v>54.6</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -545,28 +545,28 @@
         <v>1182.9</v>
       </c>
       <c r="E5">
-        <v>76.72</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>36.86</v>
       </c>
       <c r="H5">
-        <v>80.23999999999999</v>
+        <v>84</v>
       </c>
       <c r="I5">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J5">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="K5">
-        <v>46.26</v>
+        <v>53.55</v>
       </c>
       <c r="L5">
-        <v>48.56</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>44.94</v>
+        <v>49.86</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -583,7 +583,7 @@
         <v>905.96</v>
       </c>
       <c r="E6">
-        <v>77.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -592,19 +592,19 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>61.2</v>
+        <v>84</v>
       </c>
       <c r="I6">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J6">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="K6">
-        <v>43.78</v>
+        <v>48.82</v>
       </c>
       <c r="L6">
-        <v>46.11</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>41.16</v>
+        <v>44.54</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>841.54</v>
       </c>
       <c r="E7">
-        <v>73.83</v>
+        <v>75.27</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -630,19 +630,19 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>42</v>
+        <v>61.2</v>
       </c>
       <c r="I7">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J7">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="K7">
-        <v>40.05</v>
+        <v>43.55</v>
       </c>
       <c r="L7">
-        <v>42.27</v>
+        <v>45.53</v>
       </c>
     </row>
     <row r="8">
@@ -650,7 +650,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>39.48</v>
+        <v>42.72</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>1166.09</v>
       </c>
       <c r="E8">
-        <v>73.34999999999999</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -668,19 +668,19 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>42</v>
+        <v>49.38</v>
       </c>
       <c r="I8">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J8">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="K8">
-        <v>38.38</v>
+        <v>41.73</v>
       </c>
       <c r="L8">
-        <v>40.58</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>35.79</v>
+        <v>38.85</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>817.2</v>
+        <v>1214.24</v>
       </c>
       <c r="E9">
-        <v>68.63</v>
+        <v>70.69</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -709,16 +709,16 @@
         <v>42</v>
       </c>
       <c r="I9">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J9">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="K9">
-        <v>34.76</v>
+        <v>37.92</v>
       </c>
       <c r="L9">
-        <v>36.82</v>
+        <v>39.77</v>
       </c>
     </row>
     <row r="10">
@@ -726,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>35.62</v>
+        <v>38.23</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>756</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>69.56</v>
+        <v>71.47</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -747,16 +747,16 @@
         <v>42</v>
       </c>
       <c r="I10">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J10">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="K10">
-        <v>34.57</v>
+        <v>37.29</v>
       </c>
       <c r="L10">
-        <v>36.67</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>34.14</v>
+        <v>36.62</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>741.5700000000001</v>
+        <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>67.33</v>
+        <v>69.11</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -785,16 +785,16 @@
         <v>42</v>
       </c>
       <c r="I11">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J11">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="K11">
-        <v>33.12</v>
+        <v>35.71</v>
       </c>
       <c r="L11">
-        <v>35.15</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="12">
@@ -802,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>32.3</v>
+        <v>34.34</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1169.74</v>
+        <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>66.09999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -823,16 +823,16 @@
         <v>42</v>
       </c>
       <c r="I12">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J12">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="K12">
-        <v>31.3</v>
+        <v>33.45</v>
       </c>
       <c r="L12">
-        <v>33.29</v>
+        <v>35.23</v>
       </c>
     </row>
     <row r="13">
@@ -840,16 +840,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>32.8</v>
+        <v>35.17</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1072.32</v>
+        <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>67.87</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -861,16 +861,16 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J13">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="K13">
-        <v>31.78</v>
+        <v>34.25</v>
       </c>
       <c r="L13">
-        <v>33.82</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="14">
@@ -878,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>30.38</v>
+        <v>32.45</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>705.48</v>
+        <v>853.14</v>
       </c>
       <c r="E14">
-        <v>63.94</v>
+        <v>65.55</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J14">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="K14">
-        <v>29.42</v>
+        <v>31.59</v>
       </c>
       <c r="L14">
-        <v>31.34</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="15">
@@ -916,7 +916,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>29.79</v>
+        <v>31.98</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -925,7 +925,7 @@
         <v>754.67</v>
       </c>
       <c r="E15">
-        <v>64.77</v>
+        <v>66.59</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J15">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="K15">
-        <v>28.82</v>
+        <v>31.11</v>
       </c>
       <c r="L15">
-        <v>30.77</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="16">
@@ -954,7 +954,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>28.22</v>
+        <v>30.25</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>855.15</v>
       </c>
       <c r="E16">
-        <v>63.84</v>
+        <v>65.41</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J16">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="K16">
-        <v>27.26</v>
+        <v>29.39</v>
       </c>
       <c r="L16">
-        <v>29.18</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="17">
@@ -992,7 +992,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>27.59</v>
+        <v>29.37</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>754.2</v>
       </c>
       <c r="E17">
-        <v>62.59</v>
+        <v>64.31</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1013,16 +1013,16 @@
         <v>42</v>
       </c>
       <c r="I17">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J17">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="K17">
-        <v>26.65</v>
+        <v>28.53</v>
       </c>
       <c r="L17">
-        <v>28.53</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="18">
@@ -1030,16 +1030,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>26.05</v>
+        <v>27.81</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>588</v>
+        <v>656.75</v>
       </c>
       <c r="E18">
-        <v>58.89</v>
+        <v>60.93</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1048,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>31.72</v>
+        <v>42</v>
       </c>
       <c r="I18">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J18">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="K18">
-        <v>25.16</v>
+        <v>27.01</v>
       </c>
       <c r="L18">
-        <v>26.93</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="19">
@@ -1068,7 +1068,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>26.03</v>
+        <v>27.3</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>863.6799999999999</v>
       </c>
       <c r="E19">
-        <v>61.57</v>
+        <v>62.74</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>19.2</v>
+        <v>42</v>
       </c>
       <c r="I19">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J19">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="K19">
-        <v>25.1</v>
+        <v>26.47</v>
       </c>
       <c r="L19">
-        <v>26.95</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="20">
@@ -1106,7 +1106,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>24.96</v>
+        <v>26.89</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>740.58</v>
       </c>
       <c r="E20">
-        <v>59.63</v>
+        <v>61.84</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="I20">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J20">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="K20">
-        <v>24.06</v>
+        <v>26.07</v>
       </c>
       <c r="L20">
-        <v>25.86</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>23.16</v>
+        <v>24.96</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>763.54</v>
       </c>
       <c r="E21">
-        <v>56.95</v>
+        <v>59.31</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1162,19 +1162,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="I21">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J21">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="K21">
-        <v>22.31</v>
+        <v>24.19</v>
       </c>
       <c r="L21">
-        <v>24.02</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="22">
@@ -1182,7 +1182,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>24.14</v>
+        <v>25.58</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         <v>882</v>
       </c>
       <c r="E22">
-        <v>60.2</v>
+        <v>62.08</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1200,19 +1200,19 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J22">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="K22">
-        <v>23.23</v>
+        <v>24.77</v>
       </c>
       <c r="L22">
-        <v>25.04</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="23">
@@ -1220,7 +1220,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>21.85</v>
+        <v>23.25</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         <v>840</v>
       </c>
       <c r="E23">
-        <v>56.05</v>
+        <v>57.6</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J23">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="K23">
-        <v>21.01</v>
+        <v>22.49</v>
       </c>
       <c r="L23">
-        <v>22.69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -1258,7 +1258,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>22.09</v>
+        <v>23.58</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>715.7</v>
       </c>
       <c r="E24">
-        <v>57.02</v>
+        <v>58.8</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J24">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="K24">
-        <v>21.23</v>
+        <v>22.81</v>
       </c>
       <c r="L24">
-        <v>22.95</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="25">
@@ -1296,7 +1296,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>20.12</v>
+        <v>21.44</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>824.58</v>
       </c>
       <c r="E25">
-        <v>54.13</v>
+        <v>55.8</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1317,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J25">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="K25">
-        <v>19.31</v>
+        <v>20.71</v>
       </c>
       <c r="L25">
-        <v>20.94</v>
+        <v>22.17</v>
       </c>
     </row>
   </sheetData>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>96.34</v>
+        <v>102.93</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1415,28 +1415,28 @@
         <v>882</v>
       </c>
       <c r="E2">
-        <v>75.65000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="F2">
-        <v>31.72</v>
+        <v>36.86</v>
       </c>
       <c r="G2">
-        <v>42</v>
+        <v>49.38</v>
       </c>
       <c r="H2">
-        <v>84</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="I2">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J2">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="K2">
-        <v>95.2</v>
+        <v>101.91</v>
       </c>
       <c r="L2">
-        <v>97.48</v>
+        <v>103.95</v>
       </c>
     </row>
     <row r="3">
@@ -1444,7 +1444,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>68.59</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>798</v>
       </c>
       <c r="E3">
-        <v>70.20999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1465,16 +1465,16 @@
         <v>84</v>
       </c>
       <c r="I3">
-        <v>15934</v>
+        <v>21794</v>
       </c>
       <c r="J3">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="K3">
-        <v>67.5</v>
+        <v>72.69</v>
       </c>
       <c r="L3">
-        <v>69.68000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1482,7 +1482,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>65.52</v>
+        <v>70.75</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1491,7 +1491,7 @@
         <v>1008</v>
       </c>
       <c r="E4">
-        <v>70.98999999999999</v>
+        <v>72.17</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>84</v>
       </c>
       <c r="I4">
-        <v>14690</v>
+        <v>20883</v>
       </c>
       <c r="J4">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="K4">
-        <v>64.37</v>
+        <v>69.77</v>
       </c>
       <c r="L4">
-        <v>66.67</v>
+        <v>71.73</v>
       </c>
     </row>
     <row r="5">
@@ -1520,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>57.56</v>
+        <v>62.13</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1529,28 +1529,28 @@
         <v>741.86</v>
       </c>
       <c r="E5">
-        <v>65.12</v>
+        <v>66.59</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>38.39</v>
+        <v>42</v>
       </c>
       <c r="H5">
-        <v>80.23999999999999</v>
+        <v>84</v>
       </c>
       <c r="I5">
-        <v>14067</v>
+        <v>19547</v>
       </c>
       <c r="J5">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="K5">
-        <v>56.49</v>
+        <v>61.19</v>
       </c>
       <c r="L5">
-        <v>58.64</v>
+        <v>63.06</v>
       </c>
     </row>
     <row r="6">
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>56.17</v>
+        <v>60.75</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1567,28 +1567,28 @@
         <v>714</v>
       </c>
       <c r="E6">
-        <v>67.31999999999999</v>
+        <v>68.22</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>36.86</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>63.44</v>
+        <v>84</v>
       </c>
       <c r="I6">
-        <v>13705</v>
+        <v>18393</v>
       </c>
       <c r="J6">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="K6">
-        <v>55.04</v>
+        <v>59.76</v>
       </c>
       <c r="L6">
-        <v>57.3</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="7">
@@ -1596,7 +1596,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.69</v>
+        <v>57.07</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1605,28 +1605,28 @@
         <v>840</v>
       </c>
       <c r="E7">
-        <v>64.78</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>31.72</v>
+        <v>39.07</v>
       </c>
       <c r="H7">
-        <v>53.49</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I7">
-        <v>13405</v>
+        <v>17568</v>
       </c>
       <c r="J7">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="K7">
-        <v>51.6</v>
+        <v>56.09</v>
       </c>
       <c r="L7">
-        <v>53.79</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="8">
@@ -1634,37 +1634,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>51.52</v>
+        <v>56.92</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>756</v>
+        <v>1008</v>
       </c>
       <c r="E8">
-        <v>64.58</v>
+        <v>66.92</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>26.75</v>
+        <v>38.39</v>
       </c>
       <c r="H8">
-        <v>49.38</v>
+        <v>76.78</v>
       </c>
       <c r="I8">
-        <v>13143</v>
+        <v>16901</v>
       </c>
       <c r="J8">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="K8">
-        <v>50.41</v>
+        <v>55.91</v>
       </c>
       <c r="L8">
-        <v>52.62</v>
+        <v>57.93</v>
       </c>
     </row>
     <row r="9">
@@ -1672,37 +1672,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>47.48</v>
+        <v>53.49</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>798</v>
+        <v>1134</v>
       </c>
       <c r="E9">
-        <v>62.92</v>
+        <v>64.95</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>19.2</v>
+        <v>36.86</v>
       </c>
       <c r="H9">
-        <v>49.38</v>
+        <v>55.78</v>
       </c>
       <c r="I9">
-        <v>12915</v>
+        <v>16300</v>
       </c>
       <c r="J9">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="K9">
-        <v>46.39</v>
+        <v>52.49</v>
       </c>
       <c r="L9">
-        <v>48.56</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="10">
@@ -1710,37 +1710,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>48</v>
+        <v>54.43</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>756</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>62.87</v>
+        <v>65.3</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>19.2</v>
+        <v>36.86</v>
       </c>
       <c r="H10">
-        <v>49.38</v>
+        <v>63.44</v>
       </c>
       <c r="I10">
-        <v>12726</v>
+        <v>15771</v>
       </c>
       <c r="J10">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="K10">
-        <v>46.9</v>
+        <v>53.41</v>
       </c>
       <c r="L10">
-        <v>49.09</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="11">
@@ -1748,37 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>46.45</v>
+        <v>53.9</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>714</v>
+        <v>1386</v>
       </c>
       <c r="E11">
-        <v>61.57</v>
+        <v>64.08</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>19.2</v>
+        <v>36.86</v>
       </c>
       <c r="H11">
-        <v>49.38</v>
+        <v>63.44</v>
       </c>
       <c r="I11">
-        <v>12555</v>
+        <v>15227</v>
       </c>
       <c r="J11">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="K11">
-        <v>45.37</v>
+        <v>52.88</v>
       </c>
       <c r="L11">
-        <v>47.52</v>
+        <v>54.92</v>
       </c>
     </row>
     <row r="12">
@@ -1786,37 +1786,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>44.63</v>
+        <v>52.35</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>588</v>
+        <v>1554</v>
       </c>
       <c r="E12">
-        <v>60.56</v>
+        <v>63.6</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>12</v>
+        <v>31.72</v>
       </c>
       <c r="H12">
-        <v>42</v>
+        <v>53.49</v>
       </c>
       <c r="I12">
-        <v>12414</v>
+        <v>14773</v>
       </c>
       <c r="J12">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="K12">
-        <v>43.57</v>
+        <v>51.33</v>
       </c>
       <c r="L12">
-        <v>45.7</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="13">
@@ -1824,37 +1824,37 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>45.89</v>
+        <v>55.1</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>882</v>
+        <v>1218</v>
       </c>
       <c r="E13">
-        <v>62.92</v>
+        <v>66.19</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>12</v>
+        <v>36.86</v>
       </c>
       <c r="H13">
-        <v>49.38</v>
+        <v>63.44</v>
       </c>
       <c r="I13">
-        <v>12275</v>
+        <v>14336</v>
       </c>
       <c r="J13">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="K13">
-        <v>44.77</v>
+        <v>54.02</v>
       </c>
       <c r="L13">
-        <v>47</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="14">
@@ -1862,37 +1862,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>43.1</v>
+        <v>52.72</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>630</v>
+        <v>756</v>
       </c>
       <c r="E14">
-        <v>60.14</v>
+        <v>63.4</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H14">
-        <v>42</v>
+        <v>57.59</v>
       </c>
       <c r="I14">
-        <v>12101</v>
+        <v>13859</v>
       </c>
       <c r="J14">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="K14">
-        <v>42.03</v>
+        <v>51.67</v>
       </c>
       <c r="L14">
-        <v>44.17</v>
+        <v>53.78</v>
       </c>
     </row>
     <row r="15">
@@ -1900,7 +1900,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>42.76</v>
+        <v>53.54</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1909,28 +1909,28 @@
         <v>714</v>
       </c>
       <c r="E15">
-        <v>60.96</v>
+        <v>64.66</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H15">
-        <v>42</v>
+        <v>57.59</v>
       </c>
       <c r="I15">
-        <v>11975</v>
+        <v>13467</v>
       </c>
       <c r="J15">
         <v>0.5600000000000001</v>
       </c>
       <c r="K15">
-        <v>41.67</v>
+        <v>52.45</v>
       </c>
       <c r="L15">
-        <v>43.85</v>
+        <v>54.63</v>
       </c>
     </row>
     <row r="16">
@@ -1938,7 +1938,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>40.89</v>
+        <v>52.09</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1947,28 +1947,28 @@
         <v>672</v>
       </c>
       <c r="E16">
-        <v>60.11</v>
+        <v>64.11</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H16">
-        <v>42</v>
+        <v>51.73</v>
       </c>
       <c r="I16">
-        <v>11843</v>
+        <v>13057</v>
       </c>
       <c r="J16">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K16">
-        <v>39.81</v>
+        <v>50.99</v>
       </c>
       <c r="L16">
-        <v>41.97</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="17">
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>40.25</v>
+        <v>52.15</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1985,28 +1985,28 @@
         <v>588</v>
       </c>
       <c r="E17">
-        <v>60.08</v>
+        <v>64.89</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H17">
-        <v>42</v>
+        <v>49.38</v>
       </c>
       <c r="I17">
-        <v>11724</v>
+        <v>12641</v>
       </c>
       <c r="J17">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="K17">
-        <v>39.17</v>
+        <v>51.02</v>
       </c>
       <c r="L17">
-        <v>41.34</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="18">
@@ -2014,7 +2014,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>38.51</v>
+        <v>51.02</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2023,28 +2023,28 @@
         <v>678.4400000000001</v>
       </c>
       <c r="E18">
-        <v>57.61</v>
+        <v>62.05</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H18">
-        <v>42</v>
+        <v>53.49</v>
       </c>
       <c r="I18">
-        <v>11598</v>
+        <v>12240</v>
       </c>
       <c r="J18">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K18">
-        <v>37.46</v>
+        <v>49.92</v>
       </c>
       <c r="L18">
-        <v>39.55</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="19">
@@ -2052,7 +2052,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>38.95</v>
+        <v>51.64</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2061,28 +2061,28 @@
         <v>672</v>
       </c>
       <c r="E19">
-        <v>59.44</v>
+        <v>64.09</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H19">
-        <v>42</v>
+        <v>53.49</v>
       </c>
       <c r="I19">
-        <v>11478</v>
+        <v>11888</v>
       </c>
       <c r="J19">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="K19">
-        <v>37.86</v>
+        <v>50.48</v>
       </c>
       <c r="L19">
-        <v>40.04</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="20">
@@ -2090,7 +2090,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>37.6</v>
+        <v>52.39</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2099,28 +2099,28 @@
         <v>588</v>
       </c>
       <c r="E20">
-        <v>58.51</v>
+        <v>64.38</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H20">
-        <v>42</v>
+        <v>57.59</v>
       </c>
       <c r="I20">
-        <v>11364</v>
+        <v>11544</v>
       </c>
       <c r="J20">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="K20">
-        <v>36.53</v>
+        <v>51.21</v>
       </c>
       <c r="L20">
-        <v>38.68</v>
+        <v>53.56</v>
       </c>
     </row>
     <row r="21">
@@ -2128,37 +2128,37 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>35.34</v>
+        <v>50.07</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>630</v>
+        <v>672</v>
       </c>
       <c r="E21">
-        <v>55.7</v>
+        <v>62.28</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="H21">
-        <v>42</v>
+        <v>49.38</v>
       </c>
       <c r="I21">
-        <v>11251</v>
+        <v>11196</v>
       </c>
       <c r="J21">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="K21">
-        <v>34.31</v>
+        <v>48.91</v>
       </c>
       <c r="L21">
-        <v>36.37</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="22">
@@ -2166,37 +2166,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>37.23</v>
+        <v>53.09</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="E22">
-        <v>59.31</v>
+        <v>66.05</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H22">
-        <v>42</v>
+        <v>53.49</v>
       </c>
       <c r="I22">
-        <v>11131</v>
+        <v>10839</v>
       </c>
       <c r="J22">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="K22">
-        <v>36.13</v>
+        <v>51.85</v>
       </c>
       <c r="L22">
-        <v>38.33</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="23">
@@ -2204,37 +2204,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34.02</v>
+        <v>49.76</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>630</v>
+        <v>756</v>
       </c>
       <c r="E23">
-        <v>55.77</v>
+        <v>62.36</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="H23">
-        <v>42</v>
+        <v>49.38</v>
       </c>
       <c r="I23">
-        <v>10994</v>
+        <v>10485</v>
       </c>
       <c r="J23">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="K23">
-        <v>32.97</v>
+        <v>48.56</v>
       </c>
       <c r="L23">
-        <v>35.06</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="24">
@@ -2242,7 +2242,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>34.8</v>
+        <v>52.29</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>714</v>
       </c>
       <c r="E24">
-        <v>57</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="H24">
-        <v>42</v>
+        <v>53.49</v>
       </c>
       <c r="I24">
-        <v>10883</v>
+        <v>10138</v>
       </c>
       <c r="J24">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="K24">
-        <v>33.73</v>
+        <v>51.04</v>
       </c>
       <c r="L24">
-        <v>35.87</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="25">
@@ -2280,7 +2280,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>32.6</v>
+        <v>49.99</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2289,28 +2289,28 @@
         <v>770.17</v>
       </c>
       <c r="E25">
-        <v>55.47</v>
+        <v>63.64</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>19.56</v>
       </c>
       <c r="H25">
-        <v>42.79</v>
+        <v>50.31</v>
       </c>
       <c r="I25">
-        <v>10763</v>
+        <v>9825</v>
       </c>
       <c r="J25">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="K25">
-        <v>31.55</v>
+        <v>48.73</v>
       </c>
       <c r="L25">
-        <v>33.64</v>
+        <v>51.25</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_costs_OMOP.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>101.82</v>
+        <v>440.36</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1054.79</v>
+        <v>5962.38</v>
       </c>
       <c r="E2">
-        <v>102.33</v>
+        <v>477.13</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>138.38</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>305.84</v>
       </c>
       <c r="H2">
-        <v>141.59</v>
+        <v>570.76</v>
       </c>
       <c r="I2">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J2">
-        <v>0.6899999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
-        <v>100.48</v>
+        <v>434.1</v>
       </c>
       <c r="L2">
-        <v>103.16</v>
+        <v>446.62</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>71.75</v>
+        <v>287.24</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>877.74</v>
+        <v>6567.13</v>
       </c>
       <c r="E3">
-        <v>89.72</v>
+        <v>410.47</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>38.79</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>154.81</v>
       </c>
       <c r="H3">
-        <v>103.2</v>
+        <v>369.22</v>
       </c>
       <c r="I3">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J3">
-        <v>0.6</v>
+        <v>2.75</v>
       </c>
       <c r="K3">
-        <v>70.56999999999999</v>
+        <v>281.85</v>
       </c>
       <c r="L3">
-        <v>72.93000000000001</v>
+        <v>292.63</v>
       </c>
     </row>
     <row r="4">
@@ -498,37 +498,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>65.73999999999999</v>
+        <v>265.28</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1078.73</v>
+        <v>7330.06</v>
       </c>
       <c r="E4">
-        <v>89.09</v>
+        <v>424.76</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>42</v>
+        <v>121.82</v>
       </c>
       <c r="H4">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="I4">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J4">
-        <v>0.6</v>
+        <v>2.84</v>
       </c>
       <c r="K4">
-        <v>64.56999999999999</v>
+        <v>259.7</v>
       </c>
       <c r="L4">
-        <v>66.91</v>
+        <v>270.85</v>
       </c>
     </row>
     <row r="5">
@@ -536,37 +536,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>54.6</v>
+        <v>221.74</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1182.9</v>
+        <v>8512.59</v>
       </c>
       <c r="E5">
-        <v>79.84999999999999</v>
+        <v>388.38</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>36.86</v>
+        <v>84</v>
       </c>
       <c r="H5">
-        <v>84</v>
+        <v>276.33</v>
       </c>
       <c r="I5">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J5">
-        <v>0.53</v>
+        <v>2.6</v>
       </c>
       <c r="K5">
-        <v>53.55</v>
+        <v>216.64</v>
       </c>
       <c r="L5">
-        <v>55.65</v>
+        <v>226.83</v>
       </c>
     </row>
     <row r="6">
@@ -574,37 +574,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>49.86</v>
+        <v>201.4</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>905.96</v>
+        <v>40146.03</v>
       </c>
       <c r="E6">
-        <v>79.40000000000001</v>
+        <v>460.68</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>45.82</v>
       </c>
       <c r="H6">
-        <v>84</v>
+        <v>248.39</v>
       </c>
       <c r="I6">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J6">
-        <v>0.53</v>
+        <v>3.08</v>
       </c>
       <c r="K6">
-        <v>48.82</v>
+        <v>195.36</v>
       </c>
       <c r="L6">
-        <v>50.9</v>
+        <v>207.45</v>
       </c>
     </row>
     <row r="7">
@@ -612,37 +612,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>44.54</v>
+        <v>176.13</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>841.54</v>
+        <v>7348.36</v>
       </c>
       <c r="E7">
-        <v>75.27</v>
+        <v>350.13</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="H7">
-        <v>61.2</v>
+        <v>210</v>
       </c>
       <c r="I7">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J7">
-        <v>0.5</v>
+        <v>2.34</v>
       </c>
       <c r="K7">
-        <v>43.55</v>
+        <v>171.53</v>
       </c>
       <c r="L7">
-        <v>45.53</v>
+        <v>180.72</v>
       </c>
     </row>
     <row r="8">
@@ -650,37 +650,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>42.72</v>
+        <v>170.95</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1166.09</v>
+        <v>5963.68</v>
       </c>
       <c r="E8">
-        <v>75.68000000000001</v>
+        <v>353.47</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="H8">
-        <v>49.38</v>
+        <v>197.67</v>
       </c>
       <c r="I8">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J8">
-        <v>0.51</v>
+        <v>2.37</v>
       </c>
       <c r="K8">
-        <v>41.73</v>
+        <v>166.31</v>
       </c>
       <c r="L8">
-        <v>43.71</v>
+        <v>175.59</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>38.85</v>
+        <v>155.71</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1214.24</v>
+        <v>9801.309999999999</v>
       </c>
       <c r="E9">
-        <v>70.69</v>
+        <v>341</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -706,19 +706,19 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="I9">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J9">
-        <v>0.47</v>
+        <v>2.28</v>
       </c>
       <c r="K9">
-        <v>37.92</v>
+        <v>151.24</v>
       </c>
       <c r="L9">
-        <v>39.77</v>
+        <v>160.19</v>
       </c>
     </row>
     <row r="10">
@@ -726,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>38.23</v>
+        <v>152.03</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>7114.25</v>
       </c>
       <c r="E10">
-        <v>71.47</v>
+        <v>333.72</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -744,19 +744,19 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="I10">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J10">
-        <v>0.48</v>
+        <v>2.23</v>
       </c>
       <c r="K10">
-        <v>37.29</v>
+        <v>147.65</v>
       </c>
       <c r="L10">
-        <v>39.17</v>
+        <v>156.41</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>36.62</v>
+        <v>146.73</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1466.24</v>
+        <v>7057.81</v>
       </c>
       <c r="E11">
-        <v>69.11</v>
+        <v>327.65</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -782,19 +782,19 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>42</v>
+        <v>161.21</v>
       </c>
       <c r="I11">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J11">
-        <v>0.46</v>
+        <v>2.19</v>
       </c>
       <c r="K11">
-        <v>35.71</v>
+        <v>142.43</v>
       </c>
       <c r="L11">
-        <v>37.52</v>
+        <v>151.03</v>
       </c>
     </row>
     <row r="12">
@@ -802,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>34.34</v>
+        <v>140.52</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1580.75</v>
+        <v>12603.34</v>
       </c>
       <c r="E12">
-        <v>67.77</v>
+        <v>337.62</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -820,19 +820,19 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>42</v>
+        <v>131.97</v>
       </c>
       <c r="I12">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J12">
-        <v>0.45</v>
+        <v>2.26</v>
       </c>
       <c r="K12">
-        <v>33.45</v>
+        <v>136.09</v>
       </c>
       <c r="L12">
-        <v>35.23</v>
+        <v>144.95</v>
       </c>
     </row>
     <row r="13">
@@ -840,16 +840,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35.17</v>
+        <v>141.85</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1324.98</v>
+        <v>15391.43</v>
       </c>
       <c r="E13">
-        <v>70</v>
+        <v>354.36</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -858,19 +858,19 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>42</v>
+        <v>131.97</v>
       </c>
       <c r="I13">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J13">
-        <v>0.47</v>
+        <v>2.37</v>
       </c>
       <c r="K13">
-        <v>34.25</v>
+        <v>137.2</v>
       </c>
       <c r="L13">
-        <v>36.08</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="14">
@@ -878,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>32.45</v>
+        <v>128.96</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>853.14</v>
+        <v>9649</v>
       </c>
       <c r="E14">
-        <v>65.55</v>
+        <v>314.53</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -896,19 +896,19 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="I14">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J14">
-        <v>0.44</v>
+        <v>2.11</v>
       </c>
       <c r="K14">
-        <v>31.59</v>
+        <v>124.83</v>
       </c>
       <c r="L14">
-        <v>33.31</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="15">
@@ -916,16 +916,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>31.98</v>
+        <v>127.8</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>754.67</v>
+        <v>6656.94</v>
       </c>
       <c r="E15">
-        <v>66.59</v>
+        <v>316.61</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -934,19 +934,19 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>42</v>
+        <v>116.45</v>
       </c>
       <c r="I15">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J15">
-        <v>0.45</v>
+        <v>2.12</v>
       </c>
       <c r="K15">
-        <v>31.11</v>
+        <v>123.64</v>
       </c>
       <c r="L15">
-        <v>32.86</v>
+        <v>131.95</v>
       </c>
     </row>
     <row r="16">
@@ -954,16 +954,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>30.25</v>
+        <v>120.11</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>855.15</v>
+        <v>5209.28</v>
       </c>
       <c r="E16">
-        <v>65.41</v>
+        <v>304.81</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>42</v>
+        <v>92.25</v>
       </c>
       <c r="I16">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J16">
-        <v>0.44</v>
+        <v>2.04</v>
       </c>
       <c r="K16">
-        <v>29.39</v>
+        <v>116.11</v>
       </c>
       <c r="L16">
-        <v>31.11</v>
+        <v>124.11</v>
       </c>
     </row>
     <row r="17">
@@ -992,16 +992,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>29.37</v>
+        <v>116.1</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>754.2</v>
+        <v>5697.46</v>
       </c>
       <c r="E17">
-        <v>64.31</v>
+        <v>295.96</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1010,19 +1010,19 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>42</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="I17">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J17">
-        <v>0.43</v>
+        <v>1.98</v>
       </c>
       <c r="K17">
-        <v>28.53</v>
+        <v>112.21</v>
       </c>
       <c r="L17">
-        <v>30.21</v>
+        <v>119.98</v>
       </c>
     </row>
     <row r="18">
@@ -1030,16 +1030,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>27.81</v>
+        <v>112.37</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>656.75</v>
+        <v>6316.88</v>
       </c>
       <c r="E18">
-        <v>60.93</v>
+        <v>293.8</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1048,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="I18">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J18">
-        <v>0.41</v>
+        <v>1.97</v>
       </c>
       <c r="K18">
-        <v>27.01</v>
+        <v>108.52</v>
       </c>
       <c r="L18">
-        <v>28.61</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="19">
@@ -1068,16 +1068,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>27.3</v>
+        <v>110.15</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>863.6799999999999</v>
+        <v>5994.8</v>
       </c>
       <c r="E19">
-        <v>62.74</v>
+        <v>296.01</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="I19">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J19">
-        <v>0.42</v>
+        <v>1.98</v>
       </c>
       <c r="K19">
-        <v>26.47</v>
+        <v>106.27</v>
       </c>
       <c r="L19">
-        <v>28.12</v>
+        <v>114.04</v>
       </c>
     </row>
     <row r="20">
@@ -1106,16 +1106,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>26.89</v>
+        <v>108.06</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>740.58</v>
+        <v>5187</v>
       </c>
       <c r="E20">
-        <v>61.84</v>
+        <v>292.93</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>31.72</v>
+        <v>77.58</v>
       </c>
       <c r="I20">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J20">
-        <v>0.41</v>
+        <v>1.96</v>
       </c>
       <c r="K20">
-        <v>26.07</v>
+        <v>104.22</v>
       </c>
       <c r="L20">
-        <v>27.7</v>
+        <v>111.91</v>
       </c>
     </row>
     <row r="21">
@@ -1144,16 +1144,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>24.96</v>
+        <v>99.53</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>763.54</v>
+        <v>5086.36</v>
       </c>
       <c r="E21">
-        <v>59.31</v>
+        <v>273.34</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1162,19 +1162,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>19.2</v>
+        <v>51.72</v>
       </c>
       <c r="I21">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J21">
-        <v>0.4</v>
+        <v>1.83</v>
       </c>
       <c r="K21">
-        <v>24.19</v>
+        <v>95.94</v>
       </c>
       <c r="L21">
-        <v>25.74</v>
+        <v>103.11</v>
       </c>
     </row>
     <row r="22">
@@ -1182,16 +1182,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>25.58</v>
+        <v>102.15</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>882</v>
+        <v>6283.9</v>
       </c>
       <c r="E22">
-        <v>62.08</v>
+        <v>289.79</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1200,19 +1200,19 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>46.13</v>
       </c>
       <c r="I22">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J22">
-        <v>0.42</v>
+        <v>1.94</v>
       </c>
       <c r="K22">
-        <v>24.77</v>
+        <v>98.34</v>
       </c>
       <c r="L22">
-        <v>26.4</v>
+        <v>105.95</v>
       </c>
     </row>
     <row r="23">
@@ -1220,16 +1220,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>23.25</v>
+        <v>94.53</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>840</v>
+        <v>6005.02</v>
       </c>
       <c r="E23">
-        <v>57.6</v>
+        <v>276.71</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1238,19 +1238,19 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I23">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J23">
-        <v>0.39</v>
+        <v>1.85</v>
       </c>
       <c r="K23">
-        <v>22.49</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L23">
-        <v>24</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="24">
@@ -1258,16 +1258,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>23.58</v>
+        <v>95.36</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>715.7</v>
+        <v>4994.79</v>
       </c>
       <c r="E24">
-        <v>58.8</v>
+        <v>275.05</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1276,19 +1276,19 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>38.79</v>
       </c>
       <c r="I24">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J24">
-        <v>0.39</v>
+        <v>1.84</v>
       </c>
       <c r="K24">
-        <v>22.81</v>
+        <v>91.75</v>
       </c>
       <c r="L24">
-        <v>24.35</v>
+        <v>98.97</v>
       </c>
     </row>
     <row r="25">
@@ -1296,16 +1296,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>21.44</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>824.58</v>
+        <v>7422.12</v>
       </c>
       <c r="E25">
-        <v>55.8</v>
+        <v>258.67</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1314,19 +1314,19 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>7.64</v>
       </c>
       <c r="I25">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J25">
-        <v>0.37</v>
+        <v>1.73</v>
       </c>
       <c r="K25">
-        <v>20.71</v>
+        <v>82.06</v>
       </c>
       <c r="L25">
-        <v>22.17</v>
+        <v>88.84999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1406,37 +1406,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>102.93</v>
+        <v>341.21</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>882</v>
+        <v>5586</v>
       </c>
       <c r="E2">
-        <v>77.98999999999999</v>
+        <v>279.21</v>
       </c>
       <c r="F2">
-        <v>36.86</v>
+        <v>22.17</v>
       </c>
       <c r="G2">
-        <v>49.38</v>
+        <v>126</v>
       </c>
       <c r="H2">
-        <v>98.76000000000001</v>
+        <v>268.75</v>
       </c>
       <c r="I2">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J2">
-        <v>0.52</v>
+        <v>1.87</v>
       </c>
       <c r="K2">
-        <v>101.91</v>
+        <v>337.54</v>
       </c>
       <c r="L2">
-        <v>103.95</v>
+        <v>344.87</v>
       </c>
     </row>
     <row r="3">
@@ -1444,37 +1444,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>73.65000000000001</v>
+        <v>241.89</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>798</v>
+        <v>6468</v>
       </c>
       <c r="E3">
-        <v>71.90000000000001</v>
+        <v>255.79</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="H3">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="I3">
-        <v>21794</v>
+        <v>21815</v>
       </c>
       <c r="J3">
-        <v>0.49</v>
+        <v>1.73</v>
       </c>
       <c r="K3">
-        <v>72.69</v>
+        <v>238.49</v>
       </c>
       <c r="L3">
-        <v>74.59999999999999</v>
+        <v>245.28</v>
       </c>
     </row>
     <row r="4">
@@ -1482,37 +1482,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>70.75</v>
+        <v>239.94</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1008</v>
+        <v>3738</v>
       </c>
       <c r="E4">
-        <v>72.17</v>
+        <v>261.31</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="G4">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="H4">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="I4">
-        <v>20883</v>
+        <v>20900</v>
       </c>
       <c r="J4">
-        <v>0.5</v>
+        <v>1.81</v>
       </c>
       <c r="K4">
-        <v>69.77</v>
+        <v>236.4</v>
       </c>
       <c r="L4">
-        <v>71.73</v>
+        <v>243.49</v>
       </c>
     </row>
     <row r="5">
@@ -1520,37 +1520,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>62.13</v>
+        <v>213.73</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>741.86</v>
+        <v>5086.68</v>
       </c>
       <c r="E5">
-        <v>66.59</v>
+        <v>250.98</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>42</v>
+        <v>53.49</v>
       </c>
       <c r="H5">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="I5">
-        <v>19547</v>
+        <v>19555</v>
       </c>
       <c r="J5">
-        <v>0.48</v>
+        <v>1.79</v>
       </c>
       <c r="K5">
-        <v>61.19</v>
+        <v>210.21</v>
       </c>
       <c r="L5">
-        <v>63.06</v>
+        <v>217.25</v>
       </c>
     </row>
     <row r="6">
@@ -1558,37 +1558,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>60.75</v>
+        <v>212.28</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>714</v>
+        <v>40436.89</v>
       </c>
       <c r="E6">
-        <v>68.22</v>
+        <v>382.11</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="H6">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="I6">
-        <v>18393</v>
+        <v>18398</v>
       </c>
       <c r="J6">
-        <v>0.5</v>
+        <v>2.82</v>
       </c>
       <c r="K6">
-        <v>59.76</v>
+        <v>206.75</v>
       </c>
       <c r="L6">
-        <v>61.74</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="7">
@@ -1596,37 +1596,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>57.07</v>
+        <v>193.17</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>840</v>
+        <v>5259.57</v>
       </c>
       <c r="E7">
-        <v>65.70999999999999</v>
+        <v>241.73</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>39.07</v>
+        <v>42</v>
       </c>
       <c r="H7">
-        <v>76.09999999999999</v>
+        <v>168</v>
       </c>
       <c r="I7">
-        <v>17568</v>
+        <v>17573</v>
       </c>
       <c r="J7">
-        <v>0.5</v>
+        <v>1.82</v>
       </c>
       <c r="K7">
-        <v>56.09</v>
+        <v>189.6</v>
       </c>
       <c r="L7">
-        <v>58.04</v>
+        <v>196.75</v>
       </c>
     </row>
     <row r="8">
@@ -1634,37 +1634,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>56.92</v>
+        <v>196.31</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1008</v>
+        <v>4158</v>
       </c>
       <c r="E8">
-        <v>66.92</v>
+        <v>250.4</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>38.39</v>
+        <v>42</v>
       </c>
       <c r="H8">
-        <v>76.78</v>
+        <v>168</v>
       </c>
       <c r="I8">
-        <v>16901</v>
+        <v>16906</v>
       </c>
       <c r="J8">
-        <v>0.51</v>
+        <v>1.93</v>
       </c>
       <c r="K8">
-        <v>55.91</v>
+        <v>192.54</v>
       </c>
       <c r="L8">
-        <v>57.93</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="9">
@@ -1672,37 +1672,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>53.49</v>
+        <v>185.85</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1134</v>
+        <v>4536</v>
       </c>
       <c r="E9">
-        <v>64.95</v>
+        <v>244.45</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>36.86</v>
+        <v>42</v>
       </c>
       <c r="H9">
-        <v>55.78</v>
+        <v>168</v>
       </c>
       <c r="I9">
-        <v>16300</v>
+        <v>16305</v>
       </c>
       <c r="J9">
-        <v>0.51</v>
+        <v>1.91</v>
       </c>
       <c r="K9">
-        <v>52.49</v>
+        <v>182.1</v>
       </c>
       <c r="L9">
-        <v>54.49</v>
+        <v>189.6</v>
       </c>
     </row>
     <row r="10">
@@ -1710,37 +1710,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>54.43</v>
+        <v>188.06</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>3833.44</v>
       </c>
       <c r="E10">
-        <v>65.3</v>
+        <v>243.77</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>36.86</v>
+        <v>42</v>
       </c>
       <c r="H10">
-        <v>63.44</v>
+        <v>168</v>
       </c>
       <c r="I10">
-        <v>15771</v>
+        <v>15776</v>
       </c>
       <c r="J10">
-        <v>0.52</v>
+        <v>1.94</v>
       </c>
       <c r="K10">
-        <v>53.41</v>
+        <v>184.26</v>
       </c>
       <c r="L10">
-        <v>55.45</v>
+        <v>191.86</v>
       </c>
     </row>
     <row r="11">
@@ -1748,37 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>53.9</v>
+        <v>187.68</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1386</v>
+        <v>4200</v>
       </c>
       <c r="E11">
-        <v>64.08</v>
+        <v>243.6</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>36.86</v>
+        <v>42</v>
       </c>
       <c r="H11">
-        <v>63.44</v>
+        <v>168</v>
       </c>
       <c r="I11">
-        <v>15227</v>
+        <v>15232</v>
       </c>
       <c r="J11">
-        <v>0.52</v>
+        <v>1.97</v>
       </c>
       <c r="K11">
-        <v>52.88</v>
+        <v>183.81</v>
       </c>
       <c r="L11">
-        <v>54.92</v>
+        <v>191.55</v>
       </c>
     </row>
     <row r="12">
@@ -1786,37 +1786,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>52.35</v>
+        <v>184.96</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1554</v>
+        <v>5796</v>
       </c>
       <c r="E12">
-        <v>63.6</v>
+        <v>247.07</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>31.72</v>
+        <v>42</v>
       </c>
       <c r="H12">
-        <v>53.49</v>
+        <v>168</v>
       </c>
       <c r="I12">
-        <v>14773</v>
+        <v>14778</v>
       </c>
       <c r="J12">
-        <v>0.52</v>
+        <v>2.03</v>
       </c>
       <c r="K12">
-        <v>51.33</v>
+        <v>180.98</v>
       </c>
       <c r="L12">
-        <v>53.38</v>
+        <v>188.94</v>
       </c>
     </row>
     <row r="13">
@@ -1824,37 +1824,37 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>55.1</v>
+        <v>193.41</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1218</v>
+        <v>7105.28</v>
       </c>
       <c r="E13">
-        <v>66.19</v>
+        <v>255.9</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>36.86</v>
+        <v>42</v>
       </c>
       <c r="H13">
-        <v>63.44</v>
+        <v>168</v>
       </c>
       <c r="I13">
-        <v>14336</v>
+        <v>14340</v>
       </c>
       <c r="J13">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="K13">
-        <v>54.02</v>
+        <v>189.23</v>
       </c>
       <c r="L13">
-        <v>56.19</v>
+        <v>197.6</v>
       </c>
     </row>
     <row r="14">
@@ -1862,37 +1862,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>52.72</v>
+        <v>183.29</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>756</v>
+        <v>3864</v>
       </c>
       <c r="E14">
-        <v>63.4</v>
+        <v>242.37</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>31.72</v>
+        <v>42</v>
       </c>
       <c r="H14">
-        <v>57.59</v>
+        <v>168</v>
       </c>
       <c r="I14">
-        <v>13859</v>
+        <v>13862</v>
       </c>
       <c r="J14">
-        <v>0.54</v>
+        <v>2.06</v>
       </c>
       <c r="K14">
-        <v>51.67</v>
+        <v>179.25</v>
       </c>
       <c r="L14">
-        <v>53.78</v>
+        <v>187.32</v>
       </c>
     </row>
     <row r="15">
@@ -1900,37 +1900,37 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>53.54</v>
+        <v>186.44</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>714</v>
+        <v>5544</v>
       </c>
       <c r="E15">
-        <v>64.66</v>
+        <v>247.94</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>31.72</v>
+        <v>42</v>
       </c>
       <c r="H15">
-        <v>57.59</v>
+        <v>168</v>
       </c>
       <c r="I15">
-        <v>13467</v>
+        <v>13470</v>
       </c>
       <c r="J15">
-        <v>0.5600000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="K15">
-        <v>52.45</v>
+        <v>182.25</v>
       </c>
       <c r="L15">
-        <v>54.63</v>
+        <v>190.63</v>
       </c>
     </row>
     <row r="16">
@@ -1938,37 +1938,37 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>52.09</v>
+        <v>181.09</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>672</v>
+        <v>4158</v>
       </c>
       <c r="E16">
-        <v>64.11</v>
+        <v>246.59</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>31.72</v>
+        <v>38.39</v>
       </c>
       <c r="H16">
-        <v>51.73</v>
+        <v>168</v>
       </c>
       <c r="I16">
-        <v>13057</v>
+        <v>13060</v>
       </c>
       <c r="J16">
-        <v>0.5600000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="K16">
-        <v>50.99</v>
+        <v>176.86</v>
       </c>
       <c r="L16">
-        <v>53.19</v>
+        <v>185.32</v>
       </c>
     </row>
     <row r="17">
@@ -1976,37 +1976,37 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>52.15</v>
+        <v>180.25</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>588</v>
+        <v>5334</v>
       </c>
       <c r="E17">
-        <v>64.89</v>
+        <v>244.51</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>31.72</v>
+        <v>38.39</v>
       </c>
       <c r="H17">
-        <v>49.38</v>
+        <v>168</v>
       </c>
       <c r="I17">
-        <v>12641</v>
+        <v>12644</v>
       </c>
       <c r="J17">
-        <v>0.58</v>
+        <v>2.17</v>
       </c>
       <c r="K17">
-        <v>51.02</v>
+        <v>175.99</v>
       </c>
       <c r="L17">
-        <v>53.28</v>
+        <v>184.51</v>
       </c>
     </row>
     <row r="18">
@@ -2014,37 +2014,37 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>51.02</v>
+        <v>180.53</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>678.4400000000001</v>
+        <v>5712</v>
       </c>
       <c r="E18">
-        <v>62.05</v>
+        <v>246.13</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>31.72</v>
+        <v>38.39</v>
       </c>
       <c r="H18">
-        <v>53.49</v>
+        <v>168</v>
       </c>
       <c r="I18">
-        <v>12240</v>
+        <v>12243</v>
       </c>
       <c r="J18">
-        <v>0.5600000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="K18">
-        <v>49.92</v>
+        <v>176.17</v>
       </c>
       <c r="L18">
-        <v>52.11</v>
+        <v>184.89</v>
       </c>
     </row>
     <row r="19">
@@ -2052,37 +2052,37 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>51.64</v>
+        <v>180.89</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>672</v>
+        <v>3980.88</v>
       </c>
       <c r="E19">
-        <v>64.09</v>
+        <v>242.37</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>31.72</v>
+        <v>38.39</v>
       </c>
       <c r="H19">
-        <v>53.49</v>
+        <v>168</v>
       </c>
       <c r="I19">
-        <v>11888</v>
+        <v>11891</v>
       </c>
       <c r="J19">
-        <v>0.59</v>
+        <v>2.22</v>
       </c>
       <c r="K19">
-        <v>50.48</v>
+        <v>176.53</v>
       </c>
       <c r="L19">
-        <v>52.79</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="20">
@@ -2090,37 +2090,37 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>52.39</v>
+        <v>183.6</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>588</v>
+        <v>4158</v>
       </c>
       <c r="E20">
-        <v>64.38</v>
+        <v>244.27</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>31.72</v>
+        <v>38.39</v>
       </c>
       <c r="H20">
-        <v>57.59</v>
+        <v>168</v>
       </c>
       <c r="I20">
-        <v>11544</v>
+        <v>11546</v>
       </c>
       <c r="J20">
-        <v>0.6</v>
+        <v>2.27</v>
       </c>
       <c r="K20">
-        <v>51.21</v>
+        <v>179.15</v>
       </c>
       <c r="L20">
-        <v>53.56</v>
+        <v>188.06</v>
       </c>
     </row>
     <row r="21">
@@ -2128,37 +2128,37 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>50.07</v>
+        <v>174.8</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>672</v>
+        <v>3150</v>
       </c>
       <c r="E21">
-        <v>62.28</v>
+        <v>235.41</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>26.75</v>
+        <v>36</v>
       </c>
       <c r="H21">
-        <v>49.38</v>
+        <v>153.57</v>
       </c>
       <c r="I21">
-        <v>11196</v>
+        <v>11198</v>
       </c>
       <c r="J21">
-        <v>0.59</v>
+        <v>2.22</v>
       </c>
       <c r="K21">
-        <v>48.91</v>
+        <v>170.44</v>
       </c>
       <c r="L21">
-        <v>51.22</v>
+        <v>179.16</v>
       </c>
     </row>
     <row r="22">
@@ -2166,37 +2166,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>53.09</v>
+        <v>186.03</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>798</v>
+        <v>4158</v>
       </c>
       <c r="E22">
-        <v>66.05</v>
+        <v>250.21</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>31.72</v>
+        <v>38.39</v>
       </c>
       <c r="H22">
-        <v>53.49</v>
+        <v>168</v>
       </c>
       <c r="I22">
-        <v>10839</v>
+        <v>10841</v>
       </c>
       <c r="J22">
-        <v>0.63</v>
+        <v>2.4</v>
       </c>
       <c r="K22">
-        <v>51.85</v>
+        <v>181.32</v>
       </c>
       <c r="L22">
-        <v>54.33</v>
+        <v>190.74</v>
       </c>
     </row>
     <row r="23">
@@ -2204,37 +2204,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>49.76</v>
+        <v>176.54</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>756</v>
+        <v>3738</v>
       </c>
       <c r="E23">
-        <v>62.36</v>
+        <v>244.11</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>26.75</v>
+        <v>32.35</v>
       </c>
       <c r="H23">
-        <v>49.38</v>
+        <v>160.47</v>
       </c>
       <c r="I23">
-        <v>10485</v>
+        <v>10487</v>
       </c>
       <c r="J23">
-        <v>0.61</v>
+        <v>2.38</v>
       </c>
       <c r="K23">
-        <v>48.56</v>
+        <v>171.87</v>
       </c>
       <c r="L23">
-        <v>50.95</v>
+        <v>181.21</v>
       </c>
     </row>
     <row r="24">
@@ -2242,37 +2242,37 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>52.29</v>
+        <v>184.51</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>714</v>
+        <v>4423.2</v>
       </c>
       <c r="E24">
-        <v>64.31999999999999</v>
+        <v>246.48</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>31.72</v>
+        <v>38.39</v>
       </c>
       <c r="H24">
-        <v>53.49</v>
+        <v>168</v>
       </c>
       <c r="I24">
-        <v>10138</v>
+        <v>10140</v>
       </c>
       <c r="J24">
-        <v>0.64</v>
+        <v>2.45</v>
       </c>
       <c r="K24">
-        <v>51.04</v>
+        <v>179.72</v>
       </c>
       <c r="L24">
-        <v>53.55</v>
+        <v>189.31</v>
       </c>
     </row>
     <row r="25">
@@ -2280,37 +2280,37 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>49.99</v>
+        <v>174.34</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>770.17</v>
+        <v>3893.63</v>
       </c>
       <c r="E25">
-        <v>63.64</v>
+        <v>241.24</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>19.56</v>
+        <v>27.1</v>
       </c>
       <c r="H25">
-        <v>50.31</v>
+        <v>150.92</v>
       </c>
       <c r="I25">
-        <v>9825</v>
+        <v>9827</v>
       </c>
       <c r="J25">
-        <v>0.64</v>
+        <v>2.43</v>
       </c>
       <c r="K25">
-        <v>48.73</v>
+        <v>169.57</v>
       </c>
       <c r="L25">
-        <v>51.25</v>
+        <v>179.11</v>
       </c>
     </row>
   </sheetData>
